--- a/plot/storage/output/ongoing/tech_by_iso2_inst_q.xlsx
+++ b/plot/storage/output/ongoing/tech_by_iso2_inst_q.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DL36"/>
+  <dimension ref="A1:DM36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -552,67 +552,67 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
+          <t>FR | stellantis</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>SI | renault</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>SK | kia</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ES | seat</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>HU | sk innovation</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>CH | battrion</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>DE | triwo ag</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>CZ | magna energy storage</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>DE | bmz</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>FI | valmet automotive</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>IT | micro mobility</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>DE | bmw</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>SE | northvolt</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>FR | stellantis</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
@@ -917,100 +917,105 @@
       </c>
       <c r="CS1" s="1" t="inlineStr">
         <is>
-          <t>FI | finnish minerals beijing easpring</t>
-        </is>
-      </c>
-      <c r="CT1" s="1" t="inlineStr">
-        <is>
           <t>HU | eve energy</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>FR | aesc</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>GB | agratas</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>ES | hyundai mobis</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>RO | draexlmaier group</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CX1" s="1" t="inlineStr">
         <is>
           <t>SK | volvo</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="CY1" s="1" t="inlineStr">
         <is>
           <t>DE | fraunhofer ffb</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="CZ1" s="1" t="inlineStr">
         <is>
           <t>ES | aesc</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DA1" s="1" t="inlineStr">
         <is>
           <t>GB | atlantic green</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DB1" s="1" t="inlineStr">
         <is>
           <t>PL | bmz poland</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DC1" s="1" t="inlineStr">
         <is>
           <t>DE | man</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DD1" s="1" t="inlineStr">
         <is>
           <t>SK | gotion inobat batteries</t>
         </is>
       </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>PT | calb</t>
+        </is>
+      </c>
       <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>FI | finnish minerals beijing easpring</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
         <is>
           <t>GB | volklec</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>FR | tiamat</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>PT | volkswagen</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>HU | catl</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DK1" s="1" t="inlineStr">
         <is>
           <t>BG | international power supply</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DL1" s="1" t="inlineStr">
         <is>
           <t>DE | norcsi</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DM1" s="1" t="inlineStr">
         <is>
           <t>DE | siemens</t>
         </is>
@@ -1027,7 +1032,7 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>55000000</v>
+        <v>20000000</v>
       </c>
       <c r="E2" t="n">
         <v>12045000</v>
@@ -1363,6 +1368,9 @@
         <v>0</v>
       </c>
       <c r="DL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1377,7 +1385,7 @@
         <v>1000000</v>
       </c>
       <c r="D3" t="n">
-        <v>55000000</v>
+        <v>20000000</v>
       </c>
       <c r="E3" t="n">
         <v>12045000</v>
@@ -1416,7 +1424,7 @@
         <v>133333.3333333333</v>
       </c>
       <c r="Q3" t="n">
-        <v>6111111.111111111</v>
+        <v>2222222.222222222</v>
       </c>
       <c r="R3" t="n">
         <v>5347222.222222222</v>
@@ -1713,6 +1721,9 @@
         <v>0</v>
       </c>
       <c r="DL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1727,7 +1738,7 @@
         <v>1000000</v>
       </c>
       <c r="D4" t="n">
-        <v>55000000</v>
+        <v>20000000</v>
       </c>
       <c r="E4" t="n">
         <v>12045000</v>
@@ -1766,7 +1777,7 @@
         <v>200000</v>
       </c>
       <c r="Q4" t="n">
-        <v>18333333.33333333</v>
+        <v>6666666.666666666</v>
       </c>
       <c r="R4" t="n">
         <v>16041666.66666667</v>
@@ -2063,6 +2074,9 @@
         <v>0</v>
       </c>
       <c r="DL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2077,7 +2091,7 @@
         <v>1000000</v>
       </c>
       <c r="D5" t="n">
-        <v>55000000</v>
+        <v>20000000</v>
       </c>
       <c r="E5" t="n">
         <v>12045000</v>
@@ -2116,7 +2130,7 @@
         <v>200000</v>
       </c>
       <c r="Q5" t="n">
-        <v>18333333.33333333</v>
+        <v>6666666.666666666</v>
       </c>
       <c r="R5" t="n">
         <v>16041666.66666667</v>
@@ -2134,17 +2148,17 @@
         <v>12222222.22222222</v>
       </c>
       <c r="W5" t="n">
-        <v>12222222.22222222</v>
+        <v>4444444.444444444</v>
       </c>
       <c r="X5" t="n">
+        <v>1111111.111111111</v>
+      </c>
+      <c r="Y5" t="n">
         <v>6111111.111111111</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>9166666.666666666</v>
       </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
@@ -2413,6 +2427,9 @@
         <v>0</v>
       </c>
       <c r="DL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2466,7 +2483,7 @@
         <v>200000</v>
       </c>
       <c r="Q6" t="n">
-        <v>18333333.33333333</v>
+        <v>6666666.666666666</v>
       </c>
       <c r="R6" t="n">
         <v>16041666.66666667</v>
@@ -2484,23 +2501,23 @@
         <v>36666666.66666666</v>
       </c>
       <c r="W6" t="n">
+        <v>13333333.33333333</v>
+      </c>
+      <c r="X6" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>18333333.33333333</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>27500000</v>
+      </c>
+      <c r="AA6" t="n">
         <v>36666666.66666666</v>
       </c>
-      <c r="X6" t="n">
-        <v>18333333.33333333</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>27500000</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>36666666.66666666</v>
-      </c>
-      <c r="AA6" t="n">
+      <c r="AB6" t="n">
         <v>17737437.58823529</v>
       </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
       <c r="AC6" t="n">
         <v>0</v>
       </c>
@@ -2763,6 +2780,9 @@
         <v>0</v>
       </c>
       <c r="DL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2816,7 +2836,7 @@
         <v>200000</v>
       </c>
       <c r="Q7" t="n">
-        <v>18333333.33333333</v>
+        <v>6666666.666666666</v>
       </c>
       <c r="R7" t="n">
         <v>16041666.66666667</v>
@@ -2834,26 +2854,26 @@
         <v>36666666.66666666</v>
       </c>
       <c r="W7" t="n">
+        <v>13333333.33333333</v>
+      </c>
+      <c r="X7" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>18333333.33333333</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>27500000</v>
+      </c>
+      <c r="AA7" t="n">
         <v>36666666.66666666</v>
       </c>
-      <c r="X7" t="n">
-        <v>18333333.33333333</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>27500000</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>36666666.66666666</v>
-      </c>
-      <c r="AA7" t="n">
+      <c r="AB7" t="n">
         <v>53212312.76470588</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AC7" t="n">
         <v>225245.5</v>
       </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
       <c r="AD7" t="n">
         <v>0</v>
       </c>
@@ -3113,6 +3133,9 @@
         <v>0</v>
       </c>
       <c r="DL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3166,7 +3189,7 @@
         <v>200000</v>
       </c>
       <c r="Q8" t="n">
-        <v>18333333.33333333</v>
+        <v>6666666.666666666</v>
       </c>
       <c r="R8" t="n">
         <v>16041666.66666667</v>
@@ -3184,41 +3207,41 @@
         <v>36666666.66666666</v>
       </c>
       <c r="W8" t="n">
+        <v>13333333.33333333</v>
+      </c>
+      <c r="X8" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>18333333.33333333</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>27500000</v>
+      </c>
+      <c r="AA8" t="n">
         <v>36666666.66666666</v>
       </c>
-      <c r="X8" t="n">
-        <v>18333333.33333333</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>27500000</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>36666666.66666666</v>
-      </c>
-      <c r="AA8" t="n">
+      <c r="AB8" t="n">
         <v>53212312.76470588</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AC8" t="n">
         <v>225245.5</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AD8" t="n">
         <v>25700000</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AE8" t="n">
         <v>2224255.833333333</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>3333333.333333333</v>
       </c>
       <c r="AF8" t="n">
         <v>3333333.333333333</v>
       </c>
       <c r="AG8" t="n">
+        <v>3333333.333333333</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1145833.333333333</v>
       </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
@@ -3463,6 +3486,9 @@
         <v>0</v>
       </c>
       <c r="DL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3516,7 +3542,7 @@
         <v>200000</v>
       </c>
       <c r="Q9" t="n">
-        <v>18333333.33333333</v>
+        <v>6666666.666666666</v>
       </c>
       <c r="R9" t="n">
         <v>16041666.66666667</v>
@@ -3534,47 +3560,47 @@
         <v>36666666.66666666</v>
       </c>
       <c r="W9" t="n">
+        <v>13333333.33333333</v>
+      </c>
+      <c r="X9" t="n">
+        <v>14166666.66666667</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>18333333.33333333</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>27500000</v>
+      </c>
+      <c r="AA9" t="n">
         <v>36666666.66666666</v>
       </c>
-      <c r="X9" t="n">
-        <v>18333333.33333333</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>27500000</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>36666666.66666666</v>
-      </c>
-      <c r="AA9" t="n">
+      <c r="AB9" t="n">
         <v>53212312.76470588</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AC9" t="n">
         <v>225245.5</v>
       </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
       <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
         <v>6672767.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>10000000</v>
       </c>
       <c r="AF9" t="n">
         <v>10000000</v>
       </c>
       <c r="AG9" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="AH9" t="n">
         <v>3437500</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AI9" t="n">
         <v>41666666.66666666</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AJ9" t="n">
         <v>307692307.6923077</v>
       </c>
-      <c r="AJ9" t="n">
-        <v>22916666.66666667</v>
-      </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
@@ -3813,6 +3839,9 @@
         <v>0</v>
       </c>
       <c r="DL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3866,7 +3895,7 @@
         <v>200000</v>
       </c>
       <c r="Q10" t="n">
-        <v>18333333.33333333</v>
+        <v>6666666.666666666</v>
       </c>
       <c r="R10" t="n">
         <v>16041666.66666667</v>
@@ -3884,46 +3913,46 @@
         <v>36666666.66666666</v>
       </c>
       <c r="W10" t="n">
+        <v>13333333.33333333</v>
+      </c>
+      <c r="X10" t="n">
+        <v>22500000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>18333333.33333333</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>27500000</v>
+      </c>
+      <c r="AA10" t="n">
         <v>36666666.66666666</v>
       </c>
-      <c r="X10" t="n">
-        <v>18333333.33333333</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>27500000</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>36666666.66666666</v>
-      </c>
-      <c r="AA10" t="n">
+      <c r="AB10" t="n">
         <v>53212312.76470588</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AC10" t="n">
         <v>225245.5</v>
       </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
       <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
         <v>6672767.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>10000000</v>
       </c>
       <c r="AF10" t="n">
         <v>10000000</v>
       </c>
       <c r="AG10" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="AH10" t="n">
         <v>3437500</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AI10" t="n">
         <v>41666666.66666666</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AJ10" t="n">
         <v>307692307.6923077</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>68750000</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -4163,6 +4192,9 @@
         <v>0</v>
       </c>
       <c r="DL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4216,7 +4248,7 @@
         <v>200000</v>
       </c>
       <c r="Q11" t="n">
-        <v>18333333.33333333</v>
+        <v>6666666.666666666</v>
       </c>
       <c r="R11" t="n">
         <v>16041666.66666667</v>
@@ -4234,46 +4266,46 @@
         <v>36666666.66666666</v>
       </c>
       <c r="W11" t="n">
+        <v>13333333.33333333</v>
+      </c>
+      <c r="X11" t="n">
+        <v>22500000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>18333333.33333333</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>27500000</v>
+      </c>
+      <c r="AA11" t="n">
         <v>36666666.66666666</v>
       </c>
-      <c r="X11" t="n">
-        <v>18333333.33333333</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>27500000</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>36666666.66666666</v>
-      </c>
-      <c r="AA11" t="n">
+      <c r="AB11" t="n">
         <v>53212312.76470588</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AC11" t="n">
         <v>225245.5</v>
       </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
       <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
         <v>6672767.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>10000000</v>
       </c>
       <c r="AF11" t="n">
         <v>10000000</v>
       </c>
       <c r="AG11" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="AH11" t="n">
         <v>3437500</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AI11" t="n">
         <v>47222222.22222222</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AJ11" t="n">
         <v>310608974.3589743</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>68750000</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -4513,6 +4545,9 @@
         <v>0</v>
       </c>
       <c r="DL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4566,7 +4601,7 @@
         <v>200000</v>
       </c>
       <c r="Q12" t="n">
-        <v>18333333.33333333</v>
+        <v>6666666.666666666</v>
       </c>
       <c r="R12" t="n">
         <v>16041666.66666667</v>
@@ -4584,46 +4619,46 @@
         <v>36666666.66666666</v>
       </c>
       <c r="W12" t="n">
+        <v>13333333.33333333</v>
+      </c>
+      <c r="X12" t="n">
+        <v>22500000</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>18333333.33333333</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>27500000</v>
+      </c>
+      <c r="AA12" t="n">
         <v>36666666.66666666</v>
       </c>
-      <c r="X12" t="n">
-        <v>18333333.33333333</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>27500000</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>36666666.66666666</v>
-      </c>
-      <c r="AA12" t="n">
+      <c r="AB12" t="n">
         <v>53212312.76470588</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AC12" t="n">
         <v>225245.5</v>
       </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
       <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
         <v>6672767.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>10000000</v>
       </c>
       <c r="AF12" t="n">
         <v>10000000</v>
       </c>
       <c r="AG12" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="AH12" t="n">
         <v>3437500</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AI12" t="n">
         <v>58333333.33333333</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AJ12" t="n">
         <v>312067307.6923077</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>68750000</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -4863,6 +4898,9 @@
         <v>0</v>
       </c>
       <c r="DL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4916,7 +4954,7 @@
         <v>200000</v>
       </c>
       <c r="Q13" t="n">
-        <v>18333333.33333333</v>
+        <v>6666666.666666666</v>
       </c>
       <c r="R13" t="n">
         <v>16041666.66666667</v>
@@ -4934,46 +4972,46 @@
         <v>36666666.66666666</v>
       </c>
       <c r="W13" t="n">
+        <v>13333333.33333333</v>
+      </c>
+      <c r="X13" t="n">
+        <v>25833333.33333333</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>18333333.33333333</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>27500000</v>
+      </c>
+      <c r="AA13" t="n">
         <v>36666666.66666666</v>
       </c>
-      <c r="X13" t="n">
-        <v>18333333.33333333</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>27500000</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>36666666.66666666</v>
-      </c>
-      <c r="AA13" t="n">
+      <c r="AB13" t="n">
         <v>53212312.76470588</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AC13" t="n">
         <v>225245.5</v>
       </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
       <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
         <v>6672767.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>10000000</v>
       </c>
       <c r="AF13" t="n">
         <v>10000000</v>
       </c>
       <c r="AG13" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="AH13" t="n">
         <v>3437500</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AI13" t="n">
         <v>111349206.3492063</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AJ13" t="n">
         <v>312067307.6923077</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>68750000</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -5213,6 +5251,9 @@
         <v>0</v>
       </c>
       <c r="DL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5266,7 +5307,7 @@
         <v>200000</v>
       </c>
       <c r="Q14" t="n">
-        <v>18333333.33333333</v>
+        <v>6666666.666666666</v>
       </c>
       <c r="R14" t="n">
         <v>16041666.66666667</v>
@@ -5284,46 +5325,46 @@
         <v>36666666.66666666</v>
       </c>
       <c r="W14" t="n">
+        <v>13333333.33333333</v>
+      </c>
+      <c r="X14" t="n">
+        <v>32500000</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>18333333.33333333</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>27500000</v>
+      </c>
+      <c r="AA14" t="n">
         <v>36666666.66666666</v>
       </c>
-      <c r="X14" t="n">
-        <v>18333333.33333333</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>27500000</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>36666666.66666666</v>
-      </c>
-      <c r="AA14" t="n">
+      <c r="AB14" t="n">
         <v>53212312.76470588</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AC14" t="n">
         <v>225245.5</v>
       </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
       <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
         <v>6672767.5</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>10000000</v>
       </c>
       <c r="AF14" t="n">
         <v>10000000</v>
       </c>
       <c r="AG14" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="AH14" t="n">
         <v>3437500</v>
       </c>
-      <c r="AH14" t="n">
+      <c r="AI14" t="n">
         <v>180714285.7142857</v>
       </c>
-      <c r="AI14" t="n">
+      <c r="AJ14" t="n">
         <v>312067307.6923077</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>68750000</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -5563,6 +5604,9 @@
         <v>0</v>
       </c>
       <c r="DL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5616,7 +5660,7 @@
         <v>66666.66666666667</v>
       </c>
       <c r="Q15" t="n">
-        <v>12222222.22222222</v>
+        <v>4444444.444444444</v>
       </c>
       <c r="R15" t="n">
         <v>10694444.44444444</v>
@@ -5634,46 +5678,46 @@
         <v>36666666.66666666</v>
       </c>
       <c r="W15" t="n">
+        <v>13333333.33333333</v>
+      </c>
+      <c r="X15" t="n">
+        <v>32500000</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>18333333.33333333</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>27500000</v>
+      </c>
+      <c r="AA15" t="n">
         <v>36666666.66666666</v>
       </c>
-      <c r="X15" t="n">
-        <v>18333333.33333333</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>27500000</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>36666666.66666666</v>
-      </c>
-      <c r="AA15" t="n">
+      <c r="AB15" t="n">
         <v>53212312.76470588</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AC15" t="n">
         <v>225245.5</v>
       </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
       <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
         <v>6672767.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>10000000</v>
       </c>
       <c r="AF15" t="n">
         <v>10000000</v>
       </c>
       <c r="AG15" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="AH15" t="n">
         <v>3437500</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="AI15" t="n">
         <v>180714285.7142857</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AJ15" t="n">
         <v>312067307.6923077</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>68750000</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -5913,6 +5957,9 @@
         <v>0</v>
       </c>
       <c r="DL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5984,46 +6031,46 @@
         <v>36666666.66666666</v>
       </c>
       <c r="W16" t="n">
+        <v>13333333.33333333</v>
+      </c>
+      <c r="X16" t="n">
+        <v>32500000</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>18333333.33333333</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>27500000</v>
+      </c>
+      <c r="AA16" t="n">
         <v>36666666.66666666</v>
       </c>
-      <c r="X16" t="n">
-        <v>18333333.33333333</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>27500000</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>36666666.66666666</v>
-      </c>
-      <c r="AA16" t="n">
+      <c r="AB16" t="n">
         <v>53212312.76470588</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AC16" t="n">
         <v>225245.5</v>
       </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
       <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
         <v>4448511.666666667</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>10000000</v>
       </c>
       <c r="AF16" t="n">
         <v>10000000</v>
       </c>
       <c r="AG16" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="AH16" t="n">
         <v>3437500</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AI16" t="n">
         <v>180714285.7142857</v>
       </c>
-      <c r="AI16" t="n">
+      <c r="AJ16" t="n">
         <v>312067307.6923077</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>68750000</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -6263,6 +6310,9 @@
         <v>0</v>
       </c>
       <c r="DL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6334,46 +6384,46 @@
         <v>24444444.44444444</v>
       </c>
       <c r="W17" t="n">
-        <v>27500000</v>
+        <v>11944444.44444444</v>
       </c>
       <c r="X17" t="n">
+        <v>31388888.88888889</v>
+      </c>
+      <c r="Y17" t="n">
         <v>12222222.22222222</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="Z17" t="n">
         <v>18333333.33333333</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AA17" t="n">
         <v>36666666.66666666</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AB17" t="n">
         <v>53212312.76470588</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AC17" t="n">
         <v>225245.5</v>
       </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
       <c r="AD17" t="n">
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
         <v>10000000</v>
       </c>
       <c r="AG17" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="AH17" t="n">
         <v>3437500</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AI17" t="n">
         <v>180714285.7142857</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="AJ17" t="n">
         <v>312067307.6923077</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>77916666.66666667</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -6613,6 +6663,9 @@
         <v>0</v>
       </c>
       <c r="DL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6687,7 +6740,7 @@
         <v>9166666.666666666</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>29166666.66666666</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -6696,34 +6749,34 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
         <v>45792604.56521739</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AC18" t="n">
         <v>225245.5</v>
       </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
       <c r="AD18" t="n">
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
         <v>10000000</v>
       </c>
       <c r="AG18" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="AH18" t="n">
         <v>3437500</v>
       </c>
-      <c r="AH18" t="n">
+      <c r="AI18" t="n">
         <v>145793650.7936508</v>
       </c>
-      <c r="AI18" t="n">
+      <c r="AJ18" t="n">
         <v>312067307.6923077</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>96250000</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -6963,6 +7016,9 @@
         <v>0</v>
       </c>
       <c r="DL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7037,7 +7093,7 @@
         <v>9166666.666666666</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>29166666.66666666</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -7046,11 +7102,11 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
         <v>45792604.56521739</v>
       </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
       <c r="AC19" t="n">
         <v>0</v>
       </c>
@@ -7058,22 +7114,22 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
         <v>10000000</v>
       </c>
       <c r="AG19" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="AH19" t="n">
         <v>3437500</v>
       </c>
-      <c r="AH19" t="n">
+      <c r="AI19" t="n">
         <v>161666666.6666667</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AJ19" t="n">
         <v>312067307.6923077</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>96250000</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
@@ -7313,6 +7369,9 @@
         <v>0</v>
       </c>
       <c r="DL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7387,7 +7446,7 @@
         <v>45833333.33333333</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>29166666.66666666</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
@@ -7396,11 +7455,11 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
         <v>45792604.56521739</v>
       </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
       <c r="AC20" t="n">
         <v>0</v>
       </c>
@@ -7408,22 +7467,22 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>6666666.666666667</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
         <v>6666666.666666667</v>
       </c>
       <c r="AG20" t="n">
+        <v>6666666.666666667</v>
+      </c>
+      <c r="AH20" t="n">
         <v>2291666.666666667</v>
       </c>
-      <c r="AH20" t="n">
+      <c r="AI20" t="n">
         <v>161666666.6666667</v>
       </c>
-      <c r="AI20" t="n">
+      <c r="AJ20" t="n">
         <v>312067307.6923077</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>108472222.2222222</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -7663,6 +7722,9 @@
         <v>0</v>
       </c>
       <c r="DL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7737,7 +7799,7 @@
         <v>119166666.6666667</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>25000000</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -7746,11 +7808,11 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
         <v>45792604.56521739</v>
       </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
       <c r="AC21" t="n">
         <v>0</v>
       </c>
@@ -7767,13 +7829,13 @@
         <v>0</v>
       </c>
       <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
         <v>120000000</v>
       </c>
-      <c r="AI21" t="n">
+      <c r="AJ21" t="n">
         <v>361571618.025641</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>91666666.66666667</v>
       </c>
       <c r="AK21" t="n">
         <v>0</v>
@@ -8013,6 +8075,9 @@
         <v>0</v>
       </c>
       <c r="DL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8087,7 +8152,7 @@
         <v>119166666.6666667</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>16666666.66666667</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -8096,11 +8161,11 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
         <v>96511354.56521739</v>
       </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
       <c r="AC22" t="n">
         <v>0</v>
       </c>
@@ -8117,13 +8182,13 @@
         <v>0</v>
       </c>
       <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
         <v>120000000</v>
       </c>
-      <c r="AI22" t="n">
+      <c r="AJ22" t="n">
         <v>53879310.33333334</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>45833333.33333333</v>
       </c>
       <c r="AK22" t="n">
         <v>0</v>
@@ -8363,6 +8428,9 @@
         <v>0</v>
       </c>
       <c r="DL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8437,7 +8505,7 @@
         <v>119166666.6666667</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>16666666.66666667</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -8446,11 +8514,11 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
         <v>197948854.5652174</v>
       </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
       <c r="AC23" t="n">
         <v>0</v>
       </c>
@@ -8467,13 +8535,13 @@
         <v>0</v>
       </c>
       <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
         <v>117777777.7777778</v>
       </c>
-      <c r="AI23" t="n">
+      <c r="AJ23" t="n">
         <v>50962643.66666667</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>45833333.33333333</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -8713,6 +8781,9 @@
         <v>0</v>
       </c>
       <c r="DL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8787,7 +8858,7 @@
         <v>119166666.6666667</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>16666666.66666667</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -8796,11 +8867,11 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
         <v>197948854.5652174</v>
       </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
       <c r="AC24" t="n">
         <v>0</v>
       </c>
@@ -8817,13 +8888,13 @@
         <v>0</v>
       </c>
       <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
         <v>108333333.3333333</v>
       </c>
-      <c r="AI24" t="n">
+      <c r="AJ24" t="n">
         <v>49504310.33333334</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>45833333.33333333</v>
       </c>
       <c r="AK24" t="n">
         <v>0</v>
@@ -9063,6 +9134,9 @@
         <v>0</v>
       </c>
       <c r="DL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9137,7 +9211,7 @@
         <v>82499999.99999999</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>13333333.33333333</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
@@ -9146,11 +9220,11 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
         <v>197948854.5652174</v>
       </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
       <c r="AC25" t="n">
         <v>0</v>
       </c>
@@ -9167,13 +9241,13 @@
         <v>0</v>
       </c>
       <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
         <v>83888888.8888889</v>
       </c>
-      <c r="AI25" t="n">
+      <c r="AJ25" t="n">
         <v>49504310.33333334</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>45833333.33333333</v>
       </c>
       <c r="AK25" t="n">
         <v>0</v>
@@ -9413,6 +9487,9 @@
         <v>0</v>
       </c>
       <c r="DL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9487,20 +9564,20 @@
         <v>9166666.666666666</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>6666666.666666666</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
       </c>
       <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
         <v>83333333.33333333</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AB26" t="n">
         <v>197948854.5652174</v>
       </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
       <c r="AC26" t="n">
         <v>0</v>
       </c>
@@ -9517,13 +9594,13 @@
         <v>0</v>
       </c>
       <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
         <v>71666666.66666667</v>
       </c>
-      <c r="AI26" t="n">
+      <c r="AJ26" t="n">
         <v>49504310.33333334</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>45833333.33333333</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>
@@ -9763,6 +9840,9 @@
         <v>0</v>
       </c>
       <c r="DL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9837,20 +9917,20 @@
         <v>9166666.666666666</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>6666666.666666666</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
       </c>
       <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
         <v>250000000</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AB27" t="n">
         <v>197948854.5652174</v>
       </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
       <c r="AC27" t="n">
         <v>0</v>
       </c>
@@ -9867,13 +9947,13 @@
         <v>0</v>
       </c>
       <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
         <v>71666666.66666667</v>
       </c>
-      <c r="AI27" t="n">
+      <c r="AJ27" t="n">
         <v>49504310.33333334</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>45833333.33333333</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -10113,6 +10193,9 @@
         <v>0</v>
       </c>
       <c r="DL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10184,23 +10267,23 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>10006944.44444444</v>
+        <v>9472222.222222222</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>6666666.666666666</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
       </c>
       <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
         <v>295000000</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AB28" t="n">
         <v>197948854.5652174</v>
       </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
       <c r="AC28" t="n">
         <v>0</v>
       </c>
@@ -10217,13 +10300,13 @@
         <v>0</v>
       </c>
       <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
         <v>248137254.9019608</v>
       </c>
-      <c r="AI28" t="n">
+      <c r="AJ28" t="n">
         <v>49504310.33333334</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>45833333.33333333</v>
       </c>
       <c r="AK28" t="n">
         <v>0</v>
@@ -10406,7 +10489,7 @@
         <v>0</v>
       </c>
       <c r="CS28" t="n">
-        <v>44444444.44444445</v>
+        <v>0</v>
       </c>
       <c r="CT28" t="n">
         <v>0</v>
@@ -10463,6 +10546,9 @@
         <v>0</v>
       </c>
       <c r="DL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10534,23 +10620,23 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>8631944.444444444</v>
+        <v>7027777.777777778</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>6666666.666666666</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
       </c>
       <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
         <v>295000000</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AB29" t="n">
         <v>197948854.5652174</v>
       </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
       <c r="AC29" t="n">
         <v>0</v>
       </c>
@@ -10567,13 +10653,13 @@
         <v>0</v>
       </c>
       <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
         <v>284248366.0130719</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AJ29" t="n">
         <v>49504310.33333334</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>64166666.66666666</v>
       </c>
       <c r="AK29" t="n">
         <v>0</v>
@@ -10756,13 +10842,13 @@
         <v>0</v>
       </c>
       <c r="CS29" t="n">
-        <v>66666666.66666667</v>
+        <v>80881609.58333333</v>
       </c>
       <c r="CT29" t="n">
-        <v>80881609.58333333</v>
+        <v>136842105.2631579</v>
       </c>
       <c r="CU29" t="n">
-        <v>136842105.2631579</v>
+        <v>0</v>
       </c>
       <c r="CV29" t="n">
         <v>0</v>
@@ -10813,6 +10899,9 @@
         <v>0</v>
       </c>
       <c r="DL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10884,7 +10973,7 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>10854166.66666667</v>
+        <v>9250000</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
@@ -10893,14 +10982,14 @@
         <v>0</v>
       </c>
       <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
         <v>295000000</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AB30" t="n">
         <v>197948854.5652174</v>
       </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
       <c r="AC30" t="n">
         <v>0</v>
       </c>
@@ -10917,13 +11006,13 @@
         <v>0</v>
       </c>
       <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
         <v>280081699.3464052</v>
       </c>
-      <c r="AI30" t="n">
+      <c r="AJ30" t="n">
         <v>49504310.33333334</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>100833333.3333333</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
@@ -11106,16 +11195,16 @@
         <v>0</v>
       </c>
       <c r="CS30" t="n">
-        <v>66666666.66666667</v>
+        <v>80881609.58333333</v>
       </c>
       <c r="CT30" t="n">
-        <v>80881609.58333333</v>
+        <v>205263157.8947369</v>
       </c>
       <c r="CU30" t="n">
-        <v>205263157.8947369</v>
+        <v>258758991.8888889</v>
       </c>
       <c r="CV30" t="n">
-        <v>258758991.8888889</v>
+        <v>0</v>
       </c>
       <c r="CW30" t="n">
         <v>0</v>
@@ -11163,6 +11252,9 @@
         <v>0</v>
       </c>
       <c r="DL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11234,7 +11326,7 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>27520833.33333333</v>
+        <v>25916666.66666666</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
@@ -11243,14 +11335,14 @@
         <v>0</v>
       </c>
       <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
         <v>295000000</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AB31" t="n">
         <v>197948854.5652174</v>
       </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
       <c r="AC31" t="n">
         <v>0</v>
       </c>
@@ -11267,13 +11359,13 @@
         <v>0</v>
       </c>
       <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
         <v>235637254.9019608</v>
       </c>
-      <c r="AI31" t="n">
+      <c r="AJ31" t="n">
         <v>49504310.33333334</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>100833333.3333333</v>
       </c>
       <c r="AK31" t="n">
         <v>0</v>
@@ -11456,25 +11548,25 @@
         <v>0</v>
       </c>
       <c r="CS31" t="n">
-        <v>66666666.66666667</v>
+        <v>80881609.58333333</v>
       </c>
       <c r="CT31" t="n">
-        <v>80881609.58333333</v>
+        <v>205263157.8947369</v>
       </c>
       <c r="CU31" t="n">
-        <v>205263157.8947369</v>
+        <v>388138487.8333334</v>
       </c>
       <c r="CV31" t="n">
-        <v>388138487.8333334</v>
+        <v>10000000</v>
       </c>
       <c r="CW31" t="n">
-        <v>10000000</v>
+        <v>33333333.33333334</v>
       </c>
       <c r="CX31" t="n">
-        <v>33333333.33333334</v>
+        <v>100000000</v>
       </c>
       <c r="CY31" t="n">
-        <v>100000000</v>
+        <v>0</v>
       </c>
       <c r="CZ31" t="n">
         <v>0</v>
@@ -11513,6 +11605,9 @@
         <v>0</v>
       </c>
       <c r="DL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11584,23 +11679,23 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>27520833.33333333</v>
+        <v>25916666.66666666</v>
       </c>
       <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
         <v>50416666.66666667</v>
       </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
       <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
         <v>295000000</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AB32" t="n">
         <v>197948854.5652174</v>
       </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
       <c r="AC32" t="n">
         <v>0</v>
       </c>
@@ -11617,13 +11712,13 @@
         <v>0</v>
       </c>
       <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
         <v>235637254.9019608</v>
       </c>
-      <c r="AI32" t="n">
+      <c r="AJ32" t="n">
         <v>49504310.33333334</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>33611111.11111111</v>
       </c>
       <c r="AK32" t="n">
         <v>0</v>
@@ -11806,37 +11901,37 @@
         <v>0</v>
       </c>
       <c r="CS32" t="n">
-        <v>66666666.66666667</v>
+        <v>80881609.58333333</v>
       </c>
       <c r="CT32" t="n">
-        <v>80881609.58333333</v>
+        <v>205263157.8947369</v>
       </c>
       <c r="CU32" t="n">
-        <v>205263157.8947369</v>
+        <v>388138487.8333334</v>
       </c>
       <c r="CV32" t="n">
-        <v>388138487.8333334</v>
+        <v>10000000</v>
       </c>
       <c r="CW32" t="n">
-        <v>10000000</v>
+        <v>33333333.33333334</v>
       </c>
       <c r="CX32" t="n">
-        <v>33333333.33333334</v>
+        <v>100000000</v>
       </c>
       <c r="CY32" t="n">
-        <v>100000000</v>
+        <v>0</v>
       </c>
       <c r="CZ32" t="n">
-        <v>0</v>
+        <v>85310997.33333334</v>
       </c>
       <c r="DA32" t="n">
-        <v>85310997.33333334</v>
+        <v>19311307.58333334</v>
       </c>
       <c r="DB32" t="n">
-        <v>19311307.58333334</v>
+        <v>1251565.583333333</v>
       </c>
       <c r="DC32" t="n">
-        <v>1251565.583333333</v>
+        <v>0</v>
       </c>
       <c r="DD32" t="n">
         <v>0</v>
@@ -11863,6 +11958,9 @@
         <v>0</v>
       </c>
       <c r="DL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11934,23 +12032,23 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>27520833.33333333</v>
+        <v>25916666.66666666</v>
       </c>
       <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
         <v>50416666.66666667</v>
       </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
       <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
         <v>295000000</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AB33" t="n">
         <v>65982951.52173913</v>
       </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
       <c r="AC33" t="n">
         <v>0</v>
       </c>
@@ -11967,10 +12065,10 @@
         <v>0</v>
       </c>
       <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
         <v>182369281.0457516</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0</v>
       </c>
       <c r="AJ33" t="n">
         <v>0</v>
@@ -12156,43 +12254,43 @@
         <v>0</v>
       </c>
       <c r="CS33" t="n">
-        <v>66666666.66666667</v>
+        <v>80881609.58333333</v>
       </c>
       <c r="CT33" t="n">
-        <v>80881609.58333333</v>
+        <v>205263157.8947369</v>
       </c>
       <c r="CU33" t="n">
-        <v>205263157.8947369</v>
+        <v>388138487.8333334</v>
       </c>
       <c r="CV33" t="n">
-        <v>388138487.8333334</v>
+        <v>10000000</v>
       </c>
       <c r="CW33" t="n">
-        <v>10000000</v>
+        <v>33333333.33333334</v>
       </c>
       <c r="CX33" t="n">
-        <v>33333333.33333334</v>
+        <v>100000000</v>
       </c>
       <c r="CY33" t="n">
-        <v>100000000</v>
+        <v>0</v>
       </c>
       <c r="CZ33" t="n">
-        <v>0</v>
+        <v>85310997.33333334</v>
       </c>
       <c r="DA33" t="n">
-        <v>85310997.33333334</v>
+        <v>19311307.58333334</v>
       </c>
       <c r="DB33" t="n">
-        <v>19311307.58333334</v>
+        <v>1251565.583333333</v>
       </c>
       <c r="DC33" t="n">
-        <v>1251565.583333333</v>
+        <v>40000000</v>
       </c>
       <c r="DD33" t="n">
-        <v>40000000</v>
+        <v>34166666.66666666</v>
       </c>
       <c r="DE33" t="n">
-        <v>34166666.66666666</v>
+        <v>0</v>
       </c>
       <c r="DF33" t="n">
         <v>0</v>
@@ -12213,6 +12311,9 @@
         <v>0</v>
       </c>
       <c r="DL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12284,20 +12385,20 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>27520833.33333333</v>
+        <v>25916666.66666666</v>
       </c>
       <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
         <v>50416666.66666667</v>
       </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
       <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
         <v>280000000</v>
       </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
       <c r="AB34" t="n">
         <v>0</v>
       </c>
@@ -12317,10 +12418,10 @@
         <v>0</v>
       </c>
       <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
         <v>67500000</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0</v>
       </c>
       <c r="AJ34" t="n">
         <v>0</v>
@@ -12506,46 +12607,46 @@
         <v>0</v>
       </c>
       <c r="CS34" t="n">
-        <v>66666666.66666667</v>
+        <v>80881609.58333333</v>
       </c>
       <c r="CT34" t="n">
-        <v>80881609.58333333</v>
+        <v>205263157.8947369</v>
       </c>
       <c r="CU34" t="n">
-        <v>205263157.8947369</v>
+        <v>388138487.8333334</v>
       </c>
       <c r="CV34" t="n">
-        <v>388138487.8333334</v>
+        <v>10000000</v>
       </c>
       <c r="CW34" t="n">
-        <v>10000000</v>
+        <v>33333333.33333334</v>
       </c>
       <c r="CX34" t="n">
-        <v>33333333.33333334</v>
+        <v>100000000</v>
       </c>
       <c r="CY34" t="n">
-        <v>100000000</v>
+        <v>0</v>
       </c>
       <c r="CZ34" t="n">
-        <v>0</v>
+        <v>85310997.33333334</v>
       </c>
       <c r="DA34" t="n">
-        <v>85310997.33333334</v>
+        <v>19311307.58333334</v>
       </c>
       <c r="DB34" t="n">
-        <v>19311307.58333334</v>
+        <v>1251565.583333333</v>
       </c>
       <c r="DC34" t="n">
-        <v>1251565.583333333</v>
+        <v>60000000</v>
       </c>
       <c r="DD34" t="n">
-        <v>60000000</v>
+        <v>102500000</v>
       </c>
       <c r="DE34" t="n">
-        <v>102500000</v>
+        <v>111111111.1111111</v>
       </c>
       <c r="DF34" t="n">
-        <v>0</v>
+        <v>22222222.22222222</v>
       </c>
       <c r="DG34" t="n">
         <v>0</v>
@@ -12563,6 +12664,9 @@
         <v>0</v>
       </c>
       <c r="DL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12634,20 +12738,20 @@
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>27520833.33333333</v>
+        <v>25916666.66666666</v>
       </c>
       <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
         <v>50416666.66666667</v>
       </c>
-      <c r="Y35" t="n">
-        <v>0</v>
-      </c>
       <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
         <v>250000000</v>
       </c>
-      <c r="AA35" t="n">
-        <v>0</v>
-      </c>
       <c r="AB35" t="n">
         <v>0</v>
       </c>
@@ -12667,10 +12771,10 @@
         <v>0</v>
       </c>
       <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
         <v>70277777.77777778</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0</v>
       </c>
       <c r="AJ35" t="n">
         <v>0</v>
@@ -12784,7 +12888,7 @@
         <v>0</v>
       </c>
       <c r="BU35" t="n">
-        <v>11111111.11111111</v>
+        <v>50000000</v>
       </c>
       <c r="BV35" t="n">
         <v>0</v>
@@ -12856,63 +12960,66 @@
         <v>0</v>
       </c>
       <c r="CS35" t="n">
+        <v>80881609.58333333</v>
+      </c>
+      <c r="CT35" t="n">
+        <v>136842105.2631579</v>
+      </c>
+      <c r="CU35" t="n">
+        <v>388138487.8333334</v>
+      </c>
+      <c r="CV35" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="CW35" t="n">
+        <v>33333333.33333334</v>
+      </c>
+      <c r="CX35" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="CY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ35" t="n">
+        <v>85310997.33333334</v>
+      </c>
+      <c r="DA35" t="n">
+        <v>19311307.58333334</v>
+      </c>
+      <c r="DB35" t="n">
+        <v>1251565.583333333</v>
+      </c>
+      <c r="DC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD35" t="n">
+        <v>102500000</v>
+      </c>
+      <c r="DE35" t="n">
+        <v>166666666.6666667</v>
+      </c>
+      <c r="DF35" t="n">
         <v>66666666.66666667</v>
       </c>
-      <c r="CT35" t="n">
-        <v>80881609.58333333</v>
-      </c>
-      <c r="CU35" t="n">
-        <v>136842105.2631579</v>
-      </c>
-      <c r="CV35" t="n">
-        <v>388138487.8333334</v>
-      </c>
-      <c r="CW35" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="CX35" t="n">
-        <v>33333333.33333334</v>
-      </c>
-      <c r="CY35" t="n">
-        <v>100000000</v>
-      </c>
-      <c r="CZ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA35" t="n">
-        <v>85310997.33333334</v>
-      </c>
-      <c r="DB35" t="n">
-        <v>19311307.58333334</v>
-      </c>
-      <c r="DC35" t="n">
-        <v>1251565.583333333</v>
-      </c>
-      <c r="DD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="DE35" t="n">
-        <v>102500000</v>
-      </c>
-      <c r="DF35" t="n">
-        <v>0</v>
-      </c>
       <c r="DG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH35" t="n">
         <v>4666666.666666667</v>
       </c>
-      <c r="DH35" t="n">
+      <c r="DI35" t="n">
         <v>45833333.33333334</v>
       </c>
-      <c r="DI35" t="n">
+      <c r="DJ35" t="n">
         <v>405555555.5555556</v>
       </c>
-      <c r="DJ35" t="n">
+      <c r="DK35" t="n">
         <v>44964000</v>
       </c>
-      <c r="DK35" t="n">
-        <v>0</v>
-      </c>
       <c r="DL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12984,20 +13091,20 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>27520833.33333333</v>
+        <v>25916666.66666666</v>
       </c>
       <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
         <v>50416666.66666667</v>
       </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
       <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
         <v>250000000</v>
       </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
       <c r="AB36" t="n">
         <v>0</v>
       </c>
@@ -13017,11 +13124,11 @@
         <v>0</v>
       </c>
       <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
         <v>71666666.66666666</v>
       </c>
-      <c r="AI36" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ36" t="n">
         <v>0</v>
       </c>
@@ -13134,7 +13241,7 @@
         <v>0</v>
       </c>
       <c r="BU36" t="n">
-        <v>16666666.66666667</v>
+        <v>75000000</v>
       </c>
       <c r="BV36" t="n">
         <v>0</v>
@@ -13206,63 +13313,66 @@
         <v>0</v>
       </c>
       <c r="CS36" t="n">
+        <v>80881609.58333333</v>
+      </c>
+      <c r="CT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU36" t="n">
+        <v>388138487.8333334</v>
+      </c>
+      <c r="CV36" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="CW36" t="n">
+        <v>33333333.33333334</v>
+      </c>
+      <c r="CX36" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="CY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ36" t="n">
+        <v>85310997.33333334</v>
+      </c>
+      <c r="DA36" t="n">
+        <v>19311307.58333334</v>
+      </c>
+      <c r="DB36" t="n">
+        <v>1251565.583333333</v>
+      </c>
+      <c r="DC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD36" t="n">
+        <v>102500000</v>
+      </c>
+      <c r="DE36" t="n">
+        <v>166666666.6666667</v>
+      </c>
+      <c r="DF36" t="n">
         <v>66666666.66666667</v>
       </c>
-      <c r="CT36" t="n">
-        <v>80881609.58333333</v>
-      </c>
-      <c r="CU36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV36" t="n">
-        <v>388138487.8333334</v>
-      </c>
-      <c r="CW36" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="CX36" t="n">
-        <v>33333333.33333334</v>
-      </c>
-      <c r="CY36" t="n">
-        <v>100000000</v>
-      </c>
-      <c r="CZ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA36" t="n">
-        <v>85310997.33333334</v>
-      </c>
-      <c r="DB36" t="n">
-        <v>19311307.58333334</v>
-      </c>
-      <c r="DC36" t="n">
-        <v>1251565.583333333</v>
-      </c>
-      <c r="DD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="DE36" t="n">
-        <v>102500000</v>
-      </c>
-      <c r="DF36" t="n">
-        <v>0</v>
-      </c>
       <c r="DG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH36" t="n">
         <v>4666666.666666667</v>
       </c>
-      <c r="DH36" t="n">
+      <c r="DI36" t="n">
         <v>45833333.33333334</v>
       </c>
-      <c r="DI36" t="n">
+      <c r="DJ36" t="n">
         <v>608333333.3333334</v>
       </c>
-      <c r="DJ36" t="n">
+      <c r="DK36" t="n">
         <v>120000000</v>
       </c>
-      <c r="DK36" t="n">
+      <c r="DL36" t="n">
         <v>891666.6666666667</v>
       </c>
-      <c r="DL36" t="n">
+      <c r="DM36" t="n">
         <v>611111.1111111111</v>
       </c>
     </row>

--- a/plot/storage/output/ongoing/tech_by_iso2_inst_q.xlsx
+++ b/plot/storage/output/ongoing/tech_by_iso2_inst_q.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DM36"/>
+  <dimension ref="A1:DL36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,360 +662,355 @@
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>AT | energetica</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
           <t>DE | b on</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>DE | tesla</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>NL | eleo</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>PL | impact clean power technology</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>BE | volvo</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>FI | basf</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>FR | forsee power</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>IT | iveco group</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>DE | basf</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>DE | ford</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>DE | microvast</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>BE | volvo trucks</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>DE | draxlmaier</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>SK | inobat</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>PL | stellantis</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>DE | valmet automotive</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>GB | uk battery industrialisation centre</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>DE | fenecon</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>PT | acciona</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>PT | lux optimeyes energy</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>PT | projinko</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>GB | stellantis</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>DE | porsche</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>IT | sunlight group</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>LV | sia “ecolead”</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>GB | aesc</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>HU | mercedes benz</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>HU | audi</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>SE | volvo</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>ES | chery ebro</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>FR | automotive cell company</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>GB | moke international</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>RO | prime batteries technology</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>DE | gotion high tech</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>HU | bmw</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>PL | lyten</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>GB | range rover</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>DE | electricbrands</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>GR | sunlight group</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>GB | nissan</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>NO | vianode</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>FR | verkor</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>NO | freyr</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>NO | morrow batteries</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>GB | bentley</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>DE | stellantis</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>ES | volkswagen</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>HU | ecopro</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>PT | stellantis</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>DE | lion smart</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>HU | eve energy</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>FR | aesc</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>GB | agratas</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>ES | hyundai mobis</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>RO | draexlmaier group</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>SK | volvo</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CX1" s="1" t="inlineStr">
         <is>
           <t>DE | fraunhofer ffb</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="CY1" s="1" t="inlineStr">
         <is>
           <t>ES | aesc</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="CZ1" s="1" t="inlineStr">
         <is>
           <t>GB | atlantic green</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DA1" s="1" t="inlineStr">
         <is>
           <t>PL | bmz poland</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DB1" s="1" t="inlineStr">
         <is>
           <t>DE | man</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DC1" s="1" t="inlineStr">
         <is>
           <t>SK | gotion inobat batteries</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DD1" s="1" t="inlineStr">
         <is>
           <t>PT | calb</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DE1" s="1" t="inlineStr">
         <is>
           <t>FI | finnish minerals beijing easpring</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DF1" s="1" t="inlineStr">
         <is>
           <t>GB | volklec</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DG1" s="1" t="inlineStr">
         <is>
           <t>FR | tiamat</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>PT | volkswagen</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>HU | catl</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>BG | international power supply</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DK1" s="1" t="inlineStr">
         <is>
           <t>DE | norcsi</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DL1" s="1" t="inlineStr">
         <is>
           <t>DE | siemens</t>
         </is>
@@ -1370,9 +1365,6 @@
       <c r="DL2" t="n">
         <v>0</v>
       </c>
-      <c r="DM2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -1723,9 +1715,6 @@
       <c r="DL3" t="n">
         <v>0</v>
       </c>
-      <c r="DM3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -2076,9 +2065,6 @@
       <c r="DL4" t="n">
         <v>0</v>
       </c>
-      <c r="DM4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -2429,9 +2415,6 @@
       <c r="DL5" t="n">
         <v>0</v>
       </c>
-      <c r="DM5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -2782,9 +2765,6 @@
       <c r="DL6" t="n">
         <v>0</v>
       </c>
-      <c r="DM6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -3135,9 +3115,6 @@
       <c r="DL7" t="n">
         <v>0</v>
       </c>
-      <c r="DM7" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -3488,9 +3465,6 @@
       <c r="DL8" t="n">
         <v>0</v>
       </c>
-      <c r="DM8" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -3841,9 +3815,6 @@
       <c r="DL9" t="n">
         <v>0</v>
       </c>
-      <c r="DM9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -4194,9 +4165,6 @@
       <c r="DL10" t="n">
         <v>0</v>
       </c>
-      <c r="DM10" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -4547,9 +4515,6 @@
       <c r="DL11" t="n">
         <v>0</v>
       </c>
-      <c r="DM11" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -4900,9 +4865,6 @@
       <c r="DL12" t="n">
         <v>0</v>
       </c>
-      <c r="DM12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -5041,7 +5003,7 @@
         <v>3333333.333333333</v>
       </c>
       <c r="AT13" t="n">
-        <v>53.47222222222221</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
         <v>0</v>
@@ -5251,9 +5213,6 @@
         <v>0</v>
       </c>
       <c r="DL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5394,28 +5353,28 @@
         <v>3333333.333333333</v>
       </c>
       <c r="AT14" t="n">
-        <v>160.4166666666666</v>
+        <v>13750000</v>
       </c>
       <c r="AU14" t="n">
-        <v>13750000</v>
+        <v>669230769.2307692</v>
       </c>
       <c r="AV14" t="n">
-        <v>669230769.2307692</v>
+        <v>1666666.666666667</v>
       </c>
       <c r="AW14" t="n">
-        <v>1666666.666666667</v>
+        <v>6666666.666666666</v>
       </c>
       <c r="AX14" t="n">
-        <v>6666666.666666666</v>
+        <v>82500000</v>
       </c>
       <c r="AY14" t="n">
-        <v>82500000</v>
+        <v>11111111.11111111</v>
       </c>
       <c r="AZ14" t="n">
-        <v>11111111.11111111</v>
+        <v>1111111.111111111</v>
       </c>
       <c r="BA14" t="n">
-        <v>1111111.111111111</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
         <v>0</v>
@@ -5604,9 +5563,6 @@
         <v>0</v>
       </c>
       <c r="DL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5747,37 +5703,37 @@
         <v>3333333.333333333</v>
       </c>
       <c r="AT15" t="n">
-        <v>160.4166666666666</v>
+        <v>13750000</v>
       </c>
       <c r="AU15" t="n">
-        <v>13750000</v>
+        <v>669230769.2307692</v>
       </c>
       <c r="AV15" t="n">
-        <v>669230769.2307692</v>
+        <v>1666666.666666667</v>
       </c>
       <c r="AW15" t="n">
-        <v>1666666.666666667</v>
+        <v>6666666.666666666</v>
       </c>
       <c r="AX15" t="n">
-        <v>6666666.666666666</v>
+        <v>247500000</v>
       </c>
       <c r="AY15" t="n">
-        <v>247500000</v>
+        <v>33333333.33333334</v>
       </c>
       <c r="AZ15" t="n">
-        <v>33333333.33333334</v>
+        <v>3333333.333333333</v>
       </c>
       <c r="BA15" t="n">
         <v>3333333.333333333</v>
       </c>
       <c r="BB15" t="n">
-        <v>3333333.333333333</v>
+        <v>4861111.111111111</v>
       </c>
       <c r="BC15" t="n">
-        <v>4861111.111111111</v>
+        <v>61596698.33333333</v>
       </c>
       <c r="BD15" t="n">
-        <v>61596698.33333333</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>
@@ -5957,9 +5913,6 @@
         <v>0</v>
       </c>
       <c r="DL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6100,43 +6053,43 @@
         <v>3333333.333333333</v>
       </c>
       <c r="AT16" t="n">
-        <v>160.4166666666666</v>
+        <v>13750000</v>
       </c>
       <c r="AU16" t="n">
-        <v>13750000</v>
+        <v>669230769.2307692</v>
       </c>
       <c r="AV16" t="n">
-        <v>669230769.2307692</v>
+        <v>1666666.666666667</v>
       </c>
       <c r="AW16" t="n">
-        <v>1666666.666666667</v>
+        <v>6666666.666666666</v>
       </c>
       <c r="AX16" t="n">
-        <v>6666666.666666666</v>
+        <v>247500000</v>
       </c>
       <c r="AY16" t="n">
-        <v>247500000</v>
+        <v>33333333.33333334</v>
       </c>
       <c r="AZ16" t="n">
-        <v>33333333.33333334</v>
+        <v>3333333.333333333</v>
       </c>
       <c r="BA16" t="n">
         <v>3333333.333333333</v>
       </c>
       <c r="BB16" t="n">
-        <v>3333333.333333333</v>
+        <v>14583333.33333333</v>
       </c>
       <c r="BC16" t="n">
-        <v>14583333.33333333</v>
+        <v>184790095</v>
       </c>
       <c r="BD16" t="n">
-        <v>184790095</v>
+        <v>21428571.42857143</v>
       </c>
       <c r="BE16" t="n">
-        <v>21428571.42857143</v>
+        <v>6875000</v>
       </c>
       <c r="BF16" t="n">
-        <v>6875000</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -6310,9 +6263,6 @@
         <v>0</v>
       </c>
       <c r="DL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6453,52 +6403,52 @@
         <v>3333333.333333333</v>
       </c>
       <c r="AT17" t="n">
-        <v>160.4166666666666</v>
+        <v>13750000</v>
       </c>
       <c r="AU17" t="n">
-        <v>13750000</v>
+        <v>669230769.2307692</v>
       </c>
       <c r="AV17" t="n">
-        <v>669230769.2307692</v>
+        <v>1666666.666666667</v>
       </c>
       <c r="AW17" t="n">
-        <v>1666666.666666667</v>
+        <v>6666666.666666666</v>
       </c>
       <c r="AX17" t="n">
-        <v>6666666.666666666</v>
+        <v>165000000</v>
       </c>
       <c r="AY17" t="n">
-        <v>165000000</v>
+        <v>33333333.33333334</v>
       </c>
       <c r="AZ17" t="n">
-        <v>33333333.33333334</v>
+        <v>3333333.333333333</v>
       </c>
       <c r="BA17" t="n">
         <v>3333333.333333333</v>
       </c>
       <c r="BB17" t="n">
-        <v>3333333.333333333</v>
+        <v>14583333.33333333</v>
       </c>
       <c r="BC17" t="n">
-        <v>14583333.33333333</v>
+        <v>184790095</v>
       </c>
       <c r="BD17" t="n">
-        <v>184790095</v>
+        <v>21428571.42857143</v>
       </c>
       <c r="BE17" t="n">
-        <v>21428571.42857143</v>
+        <v>20625000</v>
       </c>
       <c r="BF17" t="n">
-        <v>20625000</v>
+        <v>4000000</v>
       </c>
       <c r="BG17" t="n">
-        <v>4000000</v>
+        <v>0</v>
       </c>
       <c r="BH17" t="n">
-        <v>0</v>
+        <v>6742877.56</v>
       </c>
       <c r="BI17" t="n">
-        <v>6742877.56</v>
+        <v>0</v>
       </c>
       <c r="BJ17" t="n">
         <v>0</v>
@@ -6663,9 +6613,6 @@
         <v>0</v>
       </c>
       <c r="DL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6806,58 +6753,58 @@
         <v>3333333.333333333</v>
       </c>
       <c r="AT18" t="n">
-        <v>160.4166666666666</v>
+        <v>13750000</v>
       </c>
       <c r="AU18" t="n">
-        <v>13750000</v>
+        <v>669230769.2307692</v>
       </c>
       <c r="AV18" t="n">
-        <v>669230769.2307692</v>
+        <v>1666666.666666667</v>
       </c>
       <c r="AW18" t="n">
-        <v>1666666.666666667</v>
+        <v>6666666.666666666</v>
       </c>
       <c r="AX18" t="n">
-        <v>6666666.666666666</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>33333333.33333334</v>
       </c>
       <c r="AZ18" t="n">
-        <v>33333333.33333334</v>
+        <v>3333333.333333333</v>
       </c>
       <c r="BA18" t="n">
         <v>3333333.333333333</v>
       </c>
       <c r="BB18" t="n">
-        <v>3333333.333333333</v>
+        <v>14583333.33333333</v>
       </c>
       <c r="BC18" t="n">
-        <v>14583333.33333333</v>
+        <v>184790095</v>
       </c>
       <c r="BD18" t="n">
-        <v>184790095</v>
+        <v>7142857.142857143</v>
       </c>
       <c r="BE18" t="n">
-        <v>7142857.142857143</v>
+        <v>20625000</v>
       </c>
       <c r="BF18" t="n">
-        <v>20625000</v>
+        <v>4000000</v>
       </c>
       <c r="BG18" t="n">
-        <v>4000000</v>
+        <v>0</v>
       </c>
       <c r="BH18" t="n">
-        <v>0</v>
+        <v>20228632.68</v>
       </c>
       <c r="BI18" t="n">
-        <v>20228632.68</v>
+        <v>0</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>147392290</v>
       </c>
       <c r="BK18" t="n">
-        <v>147392290</v>
+        <v>0</v>
       </c>
       <c r="BL18" t="n">
         <v>0</v>
@@ -7016,9 +6963,6 @@
         <v>0</v>
       </c>
       <c r="DL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7159,61 +7103,61 @@
         <v>3333333.333333333</v>
       </c>
       <c r="AT19" t="n">
-        <v>160.4166666666666</v>
+        <v>13750000</v>
       </c>
       <c r="AU19" t="n">
-        <v>13750000</v>
+        <v>669230769.2307692</v>
       </c>
       <c r="AV19" t="n">
-        <v>669230769.2307692</v>
+        <v>1666666.666666667</v>
       </c>
       <c r="AW19" t="n">
-        <v>1666666.666666667</v>
+        <v>6666666.666666666</v>
       </c>
       <c r="AX19" t="n">
-        <v>6666666.666666666</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>33333333.33333334</v>
       </c>
       <c r="AZ19" t="n">
-        <v>33333333.33333334</v>
+        <v>3333333.333333333</v>
       </c>
       <c r="BA19" t="n">
         <v>3333333.333333333</v>
       </c>
       <c r="BB19" t="n">
-        <v>3333333.333333333</v>
+        <v>14583333.33333333</v>
       </c>
       <c r="BC19" t="n">
-        <v>14583333.33333333</v>
+        <v>184790095</v>
       </c>
       <c r="BD19" t="n">
-        <v>184790095</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>20625000</v>
       </c>
       <c r="BF19" t="n">
-        <v>20625000</v>
+        <v>4000000</v>
       </c>
       <c r="BG19" t="n">
-        <v>4000000</v>
+        <v>0</v>
       </c>
       <c r="BH19" t="n">
-        <v>0</v>
+        <v>20228632.68</v>
       </c>
       <c r="BI19" t="n">
-        <v>20228632.68</v>
+        <v>0</v>
       </c>
       <c r="BJ19" t="n">
         <v>0</v>
       </c>
       <c r="BK19" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="BL19" t="n">
-        <v>5000000</v>
+        <v>277777.7777777778</v>
       </c>
       <c r="BM19" t="n">
         <v>277777.7777777778</v>
@@ -7222,7 +7166,7 @@
         <v>277777.7777777778</v>
       </c>
       <c r="BO19" t="n">
-        <v>277777.7777777778</v>
+        <v>0</v>
       </c>
       <c r="BP19" t="n">
         <v>0</v>
@@ -7369,9 +7313,6 @@
         <v>0</v>
       </c>
       <c r="DL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7512,61 +7453,61 @@
         <v>3333333.333333333</v>
       </c>
       <c r="AT20" t="n">
-        <v>160.4166666666666</v>
+        <v>13750000</v>
       </c>
       <c r="AU20" t="n">
-        <v>13750000</v>
+        <v>669230769.2307692</v>
       </c>
       <c r="AV20" t="n">
-        <v>669230769.2307692</v>
+        <v>1666666.666666667</v>
       </c>
       <c r="AW20" t="n">
-        <v>1666666.666666667</v>
+        <v>6666666.666666666</v>
       </c>
       <c r="AX20" t="n">
-        <v>6666666.666666666</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>33333333.33333334</v>
       </c>
       <c r="AZ20" t="n">
-        <v>33333333.33333334</v>
+        <v>3333333.333333333</v>
       </c>
       <c r="BA20" t="n">
         <v>3333333.333333333</v>
       </c>
       <c r="BB20" t="n">
-        <v>3333333.333333333</v>
+        <v>14583333.33333333</v>
       </c>
       <c r="BC20" t="n">
-        <v>14583333.33333333</v>
+        <v>184790095</v>
       </c>
       <c r="BD20" t="n">
-        <v>184790095</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>20625000</v>
       </c>
       <c r="BF20" t="n">
-        <v>20625000</v>
+        <v>4000000</v>
       </c>
       <c r="BG20" t="n">
-        <v>4000000</v>
+        <v>0</v>
       </c>
       <c r="BH20" t="n">
-        <v>0</v>
+        <v>20228632.68</v>
       </c>
       <c r="BI20" t="n">
-        <v>20228632.68</v>
+        <v>0</v>
       </c>
       <c r="BJ20" t="n">
         <v>0</v>
       </c>
       <c r="BK20" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="BL20" t="n">
-        <v>5000000</v>
+        <v>416666.6666666666</v>
       </c>
       <c r="BM20" t="n">
         <v>416666.6666666666</v>
@@ -7575,19 +7516,19 @@
         <v>416666.6666666666</v>
       </c>
       <c r="BO20" t="n">
-        <v>416666.6666666666</v>
+        <v>32468305.63636363</v>
       </c>
       <c r="BP20" t="n">
-        <v>32468305.63636363</v>
+        <v>11111.11111111111</v>
       </c>
       <c r="BQ20" t="n">
-        <v>11111.11111111111</v>
+        <v>1388888.888888889</v>
       </c>
       <c r="BR20" t="n">
-        <v>1388888.888888889</v>
+        <v>121111.1111111111</v>
       </c>
       <c r="BS20" t="n">
-        <v>121111.1111111111</v>
+        <v>0</v>
       </c>
       <c r="BT20" t="n">
         <v>0</v>
@@ -7722,9 +7663,6 @@
         <v>0</v>
       </c>
       <c r="DL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7865,61 +7803,61 @@
         <v>3333333.333333333</v>
       </c>
       <c r="AT21" t="n">
-        <v>160.4166666666666</v>
+        <v>13750000</v>
       </c>
       <c r="AU21" t="n">
-        <v>13750000</v>
+        <v>669230769.2307692</v>
       </c>
       <c r="AV21" t="n">
-        <v>669230769.2307692</v>
+        <v>1666666.666666667</v>
       </c>
       <c r="AW21" t="n">
-        <v>1666666.666666667</v>
+        <v>6666666.666666666</v>
       </c>
       <c r="AX21" t="n">
-        <v>6666666.666666666</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>33333333.33333334</v>
       </c>
       <c r="AZ21" t="n">
-        <v>33333333.33333334</v>
+        <v>3333333.333333333</v>
       </c>
       <c r="BA21" t="n">
         <v>3333333.333333333</v>
       </c>
       <c r="BB21" t="n">
-        <v>3333333.333333333</v>
+        <v>14583333.33333333</v>
       </c>
       <c r="BC21" t="n">
-        <v>14583333.33333333</v>
+        <v>184790095</v>
       </c>
       <c r="BD21" t="n">
-        <v>184790095</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>20625000</v>
       </c>
       <c r="BF21" t="n">
-        <v>20625000</v>
+        <v>4000000</v>
       </c>
       <c r="BG21" t="n">
-        <v>4000000</v>
+        <v>0</v>
       </c>
       <c r="BH21" t="n">
-        <v>0</v>
+        <v>20228632.68</v>
       </c>
       <c r="BI21" t="n">
-        <v>20228632.68</v>
+        <v>0</v>
       </c>
       <c r="BJ21" t="n">
         <v>0</v>
       </c>
       <c r="BK21" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="BL21" t="n">
-        <v>5000000</v>
+        <v>416666.6666666666</v>
       </c>
       <c r="BM21" t="n">
         <v>416666.6666666666</v>
@@ -7928,31 +7866,31 @@
         <v>416666.6666666666</v>
       </c>
       <c r="BO21" t="n">
-        <v>416666.6666666666</v>
+        <v>32468305.63636363</v>
       </c>
       <c r="BP21" t="n">
-        <v>32468305.63636363</v>
+        <v>16666.66666666667</v>
       </c>
       <c r="BQ21" t="n">
-        <v>16666.66666666667</v>
+        <v>4166666.666666667</v>
       </c>
       <c r="BR21" t="n">
-        <v>4166666.666666667</v>
+        <v>363333.3333333333</v>
       </c>
       <c r="BS21" t="n">
-        <v>363333.3333333333</v>
+        <v>59144455.75</v>
       </c>
       <c r="BT21" t="n">
-        <v>59144455.75</v>
+        <v>100000000</v>
       </c>
       <c r="BU21" t="n">
-        <v>100000000</v>
+        <v>3500000</v>
       </c>
       <c r="BV21" t="n">
-        <v>3500000</v>
+        <v>18333333.33333333</v>
       </c>
       <c r="BW21" t="n">
-        <v>18333333.33333333</v>
+        <v>0</v>
       </c>
       <c r="BX21" t="n">
         <v>0</v>
@@ -8075,9 +8013,6 @@
         <v>0</v>
       </c>
       <c r="DL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8218,61 +8153,61 @@
         <v>3333333.333333333</v>
       </c>
       <c r="AT22" t="n">
-        <v>160.4166666666666</v>
+        <v>13750000</v>
       </c>
       <c r="AU22" t="n">
-        <v>13750000</v>
+        <v>446153846.1538461</v>
       </c>
       <c r="AV22" t="n">
-        <v>446153846.1538461</v>
+        <v>1666666.666666667</v>
       </c>
       <c r="AW22" t="n">
-        <v>1666666.666666667</v>
+        <v>6666666.666666666</v>
       </c>
       <c r="AX22" t="n">
-        <v>6666666.666666666</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>33333333.33333334</v>
       </c>
       <c r="AZ22" t="n">
-        <v>33333333.33333334</v>
+        <v>3333333.333333333</v>
       </c>
       <c r="BA22" t="n">
         <v>3333333.333333333</v>
       </c>
       <c r="BB22" t="n">
-        <v>3333333.333333333</v>
+        <v>14583333.33333333</v>
       </c>
       <c r="BC22" t="n">
-        <v>14583333.33333333</v>
+        <v>184790095</v>
       </c>
       <c r="BD22" t="n">
-        <v>184790095</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>20625000</v>
       </c>
       <c r="BF22" t="n">
-        <v>20625000</v>
+        <v>4000000</v>
       </c>
       <c r="BG22" t="n">
-        <v>4000000</v>
+        <v>0</v>
       </c>
       <c r="BH22" t="n">
-        <v>0</v>
+        <v>20228632.68</v>
       </c>
       <c r="BI22" t="n">
-        <v>20228632.68</v>
+        <v>0</v>
       </c>
       <c r="BJ22" t="n">
         <v>0</v>
       </c>
       <c r="BK22" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="BL22" t="n">
-        <v>5000000</v>
+        <v>416666.6666666666</v>
       </c>
       <c r="BM22" t="n">
         <v>416666.6666666666</v>
@@ -8281,31 +8216,31 @@
         <v>416666.6666666666</v>
       </c>
       <c r="BO22" t="n">
-        <v>416666.6666666666</v>
+        <v>32468305.63636363</v>
       </c>
       <c r="BP22" t="n">
-        <v>32468305.63636363</v>
+        <v>16666.66666666667</v>
       </c>
       <c r="BQ22" t="n">
-        <v>16666.66666666667</v>
+        <v>4166666.666666667</v>
       </c>
       <c r="BR22" t="n">
-        <v>4166666.666666667</v>
+        <v>363333.3333333333</v>
       </c>
       <c r="BS22" t="n">
-        <v>363333.3333333333</v>
+        <v>59144455.75</v>
       </c>
       <c r="BT22" t="n">
-        <v>59144455.75</v>
+        <v>0</v>
       </c>
       <c r="BU22" t="n">
-        <v>0</v>
+        <v>10500000</v>
       </c>
       <c r="BV22" t="n">
-        <v>10500000</v>
+        <v>55000000</v>
       </c>
       <c r="BW22" t="n">
-        <v>55000000</v>
+        <v>0</v>
       </c>
       <c r="BX22" t="n">
         <v>0</v>
@@ -8428,9 +8363,6 @@
         <v>0</v>
       </c>
       <c r="DL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8571,61 +8503,61 @@
         <v>3333333.333333333</v>
       </c>
       <c r="AT23" t="n">
-        <v>160.4166666666666</v>
+        <v>13750000</v>
       </c>
       <c r="AU23" t="n">
-        <v>13750000</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>1666666.666666667</v>
       </c>
       <c r="AW23" t="n">
-        <v>1666666.666666667</v>
+        <v>6666666.666666666</v>
       </c>
       <c r="AX23" t="n">
-        <v>6666666.666666666</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>33333333.33333334</v>
       </c>
       <c r="AZ23" t="n">
-        <v>33333333.33333334</v>
+        <v>3333333.333333333</v>
       </c>
       <c r="BA23" t="n">
         <v>3333333.333333333</v>
       </c>
       <c r="BB23" t="n">
-        <v>3333333.333333333</v>
+        <v>14583333.33333333</v>
       </c>
       <c r="BC23" t="n">
-        <v>14583333.33333333</v>
+        <v>184790095</v>
       </c>
       <c r="BD23" t="n">
-        <v>184790095</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>20625000</v>
       </c>
       <c r="BF23" t="n">
-        <v>20625000</v>
+        <v>4000000</v>
       </c>
       <c r="BG23" t="n">
-        <v>4000000</v>
+        <v>0</v>
       </c>
       <c r="BH23" t="n">
-        <v>0</v>
+        <v>20228632.68</v>
       </c>
       <c r="BI23" t="n">
-        <v>20228632.68</v>
+        <v>0</v>
       </c>
       <c r="BJ23" t="n">
         <v>0</v>
       </c>
       <c r="BK23" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="BL23" t="n">
-        <v>5000000</v>
+        <v>416666.6666666666</v>
       </c>
       <c r="BM23" t="n">
         <v>416666.6666666666</v>
@@ -8634,52 +8566,52 @@
         <v>416666.6666666666</v>
       </c>
       <c r="BO23" t="n">
-        <v>416666.6666666666</v>
+        <v>21645537.09090909</v>
       </c>
       <c r="BP23" t="n">
-        <v>21645537.09090909</v>
+        <v>33350000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>33350000</v>
+        <v>4166666.666666667</v>
       </c>
       <c r="BR23" t="n">
-        <v>4166666.666666667</v>
+        <v>363333.3333333333</v>
       </c>
       <c r="BS23" t="n">
-        <v>363333.3333333333</v>
+        <v>59144455.75</v>
       </c>
       <c r="BT23" t="n">
-        <v>59144455.75</v>
+        <v>0</v>
       </c>
       <c r="BU23" t="n">
-        <v>0</v>
+        <v>10500000</v>
       </c>
       <c r="BV23" t="n">
-        <v>10500000</v>
+        <v>55000000</v>
       </c>
       <c r="BW23" t="n">
-        <v>55000000</v>
+        <v>11111111.11111111</v>
       </c>
       <c r="BX23" t="n">
-        <v>11111111.11111111</v>
+        <v>196153846.1538461</v>
       </c>
       <c r="BY23" t="n">
-        <v>196153846.1538461</v>
+        <v>229166.6666666667</v>
       </c>
       <c r="BZ23" t="n">
-        <v>229166.6666666667</v>
+        <v>12777777.77777778</v>
       </c>
       <c r="CA23" t="n">
-        <v>12777777.77777778</v>
+        <v>13333333.33333333</v>
       </c>
       <c r="CB23" t="n">
-        <v>13333333.33333333</v>
+        <v>41025641.02564102</v>
       </c>
       <c r="CC23" t="n">
-        <v>41025641.02564102</v>
+        <v>6666666.666666667</v>
       </c>
       <c r="CD23" t="n">
-        <v>6666666.666666667</v>
+        <v>0</v>
       </c>
       <c r="CE23" t="n">
         <v>0</v>
@@ -8781,9 +8713,6 @@
         <v>0</v>
       </c>
       <c r="DL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8924,61 +8853,61 @@
         <v>3333333.333333333</v>
       </c>
       <c r="AT24" t="n">
-        <v>160.4166666666666</v>
+        <v>13750000</v>
       </c>
       <c r="AU24" t="n">
-        <v>13750000</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>1666666.666666667</v>
       </c>
       <c r="AW24" t="n">
-        <v>1666666.666666667</v>
+        <v>6666666.666666666</v>
       </c>
       <c r="AX24" t="n">
-        <v>6666666.666666666</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>33333333.33333334</v>
       </c>
       <c r="AZ24" t="n">
-        <v>33333333.33333334</v>
+        <v>3333333.333333333</v>
       </c>
       <c r="BA24" t="n">
         <v>3333333.333333333</v>
       </c>
       <c r="BB24" t="n">
-        <v>3333333.333333333</v>
+        <v>14583333.33333333</v>
       </c>
       <c r="BC24" t="n">
-        <v>14583333.33333333</v>
+        <v>184790095</v>
       </c>
       <c r="BD24" t="n">
-        <v>184790095</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>20625000</v>
       </c>
       <c r="BF24" t="n">
-        <v>20625000</v>
+        <v>4000000</v>
       </c>
       <c r="BG24" t="n">
-        <v>4000000</v>
+        <v>0</v>
       </c>
       <c r="BH24" t="n">
-        <v>0</v>
+        <v>20228632.68</v>
       </c>
       <c r="BI24" t="n">
-        <v>20228632.68</v>
+        <v>0</v>
       </c>
       <c r="BJ24" t="n">
         <v>0</v>
       </c>
       <c r="BK24" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="BL24" t="n">
-        <v>5000000</v>
+        <v>416666.6666666666</v>
       </c>
       <c r="BM24" t="n">
         <v>416666.6666666666</v>
@@ -8987,67 +8916,67 @@
         <v>416666.6666666666</v>
       </c>
       <c r="BO24" t="n">
-        <v>416666.6666666666</v>
+        <v>0</v>
       </c>
       <c r="BP24" t="n">
-        <v>0</v>
+        <v>50016666.66666666</v>
       </c>
       <c r="BQ24" t="n">
-        <v>50016666.66666666</v>
+        <v>4166666.666666667</v>
       </c>
       <c r="BR24" t="n">
-        <v>4166666.666666667</v>
+        <v>363333.3333333333</v>
       </c>
       <c r="BS24" t="n">
-        <v>363333.3333333333</v>
+        <v>59144455.75</v>
       </c>
       <c r="BT24" t="n">
-        <v>59144455.75</v>
+        <v>0</v>
       </c>
       <c r="BU24" t="n">
-        <v>0</v>
+        <v>10500000</v>
       </c>
       <c r="BV24" t="n">
-        <v>10500000</v>
+        <v>55000000</v>
       </c>
       <c r="BW24" t="n">
-        <v>55000000</v>
+        <v>11111111.11111111</v>
       </c>
       <c r="BX24" t="n">
-        <v>11111111.11111111</v>
+        <v>196153846.1538461</v>
       </c>
       <c r="BY24" t="n">
-        <v>196153846.1538461</v>
+        <v>229166.6666666667</v>
       </c>
       <c r="BZ24" t="n">
-        <v>229166.6666666667</v>
+        <v>19166666.66666667</v>
       </c>
       <c r="CA24" t="n">
-        <v>19166666.66666667</v>
+        <v>40000000</v>
       </c>
       <c r="CB24" t="n">
-        <v>40000000</v>
+        <v>123076923.0769231</v>
       </c>
       <c r="CC24" t="n">
-        <v>123076923.0769231</v>
+        <v>20000000</v>
       </c>
       <c r="CD24" t="n">
-        <v>20000000</v>
+        <v>27500000</v>
       </c>
       <c r="CE24" t="n">
-        <v>27500000</v>
+        <v>9166666.666666666</v>
       </c>
       <c r="CF24" t="n">
-        <v>9166666.666666666</v>
+        <v>5555555.555555556</v>
       </c>
       <c r="CG24" t="n">
-        <v>5555555.555555556</v>
+        <v>12849225.88888889</v>
       </c>
       <c r="CH24" t="n">
-        <v>12849225.88888889</v>
+        <v>7800000</v>
       </c>
       <c r="CI24" t="n">
-        <v>7800000</v>
+        <v>0</v>
       </c>
       <c r="CJ24" t="n">
         <v>0</v>
@@ -9134,9 +9063,6 @@
         <v>0</v>
       </c>
       <c r="DL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9277,61 +9203,61 @@
         <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>106.9444444444444</v>
+        <v>13750000</v>
       </c>
       <c r="AU25" t="n">
-        <v>13750000</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>1666666.666666667</v>
       </c>
       <c r="AW25" t="n">
-        <v>1666666.666666667</v>
+        <v>6666666.666666666</v>
       </c>
       <c r="AX25" t="n">
-        <v>6666666.666666666</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>33333333.33333334</v>
       </c>
       <c r="AZ25" t="n">
-        <v>33333333.33333334</v>
+        <v>3333333.333333333</v>
       </c>
       <c r="BA25" t="n">
         <v>3333333.333333333</v>
       </c>
       <c r="BB25" t="n">
-        <v>3333333.333333333</v>
+        <v>14583333.33333333</v>
       </c>
       <c r="BC25" t="n">
-        <v>14583333.33333333</v>
+        <v>184790095</v>
       </c>
       <c r="BD25" t="n">
-        <v>184790095</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>20625000</v>
       </c>
       <c r="BF25" t="n">
-        <v>20625000</v>
+        <v>4000000</v>
       </c>
       <c r="BG25" t="n">
-        <v>4000000</v>
+        <v>0</v>
       </c>
       <c r="BH25" t="n">
-        <v>0</v>
+        <v>20228632.68</v>
       </c>
       <c r="BI25" t="n">
-        <v>20228632.68</v>
+        <v>0</v>
       </c>
       <c r="BJ25" t="n">
         <v>0</v>
       </c>
       <c r="BK25" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="BL25" t="n">
-        <v>5000000</v>
+        <v>416666.6666666666</v>
       </c>
       <c r="BM25" t="n">
         <v>416666.6666666666</v>
@@ -9340,76 +9266,76 @@
         <v>416666.6666666666</v>
       </c>
       <c r="BO25" t="n">
-        <v>416666.6666666666</v>
+        <v>0</v>
       </c>
       <c r="BP25" t="n">
-        <v>0</v>
+        <v>50016666.66666666</v>
       </c>
       <c r="BQ25" t="n">
-        <v>50016666.66666666</v>
+        <v>4166666.666666667</v>
       </c>
       <c r="BR25" t="n">
-        <v>4166666.666666667</v>
+        <v>363333.3333333333</v>
       </c>
       <c r="BS25" t="n">
-        <v>363333.3333333333</v>
+        <v>59144455.75</v>
       </c>
       <c r="BT25" t="n">
-        <v>59144455.75</v>
+        <v>0</v>
       </c>
       <c r="BU25" t="n">
-        <v>0</v>
+        <v>10500000</v>
       </c>
       <c r="BV25" t="n">
-        <v>10500000</v>
+        <v>55000000</v>
       </c>
       <c r="BW25" t="n">
-        <v>55000000</v>
+        <v>11111111.11111111</v>
       </c>
       <c r="BX25" t="n">
-        <v>11111111.11111111</v>
+        <v>196153846.1538461</v>
       </c>
       <c r="BY25" t="n">
-        <v>196153846.1538461</v>
+        <v>229166.6666666667</v>
       </c>
       <c r="BZ25" t="n">
-        <v>229166.6666666667</v>
+        <v>19166666.66666667</v>
       </c>
       <c r="CA25" t="n">
-        <v>19166666.66666667</v>
+        <v>40000000</v>
       </c>
       <c r="CB25" t="n">
-        <v>40000000</v>
+        <v>146606334.841629</v>
       </c>
       <c r="CC25" t="n">
-        <v>146606334.841629</v>
+        <v>20000000</v>
       </c>
       <c r="CD25" t="n">
-        <v>20000000</v>
+        <v>27500000</v>
       </c>
       <c r="CE25" t="n">
-        <v>27500000</v>
+        <v>13750000</v>
       </c>
       <c r="CF25" t="n">
-        <v>13750000</v>
+        <v>8333333.333333334</v>
       </c>
       <c r="CG25" t="n">
-        <v>8333333.333333334</v>
+        <v>38547677.66666666</v>
       </c>
       <c r="CH25" t="n">
-        <v>38547677.66666666</v>
+        <v>23400000</v>
       </c>
       <c r="CI25" t="n">
-        <v>23400000</v>
+        <v>8333333.333333333</v>
       </c>
       <c r="CJ25" t="n">
-        <v>8333333.333333333</v>
+        <v>147988649.2380952</v>
       </c>
       <c r="CK25" t="n">
-        <v>147988649.2380952</v>
+        <v>40666666.66666666</v>
       </c>
       <c r="CL25" t="n">
-        <v>40666666.66666666</v>
+        <v>0</v>
       </c>
       <c r="CM25" t="n">
         <v>0</v>
@@ -9487,9 +9413,6 @@
         <v>0</v>
       </c>
       <c r="DL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9645,31 +9568,31 @@
         <v>0</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>22222222.22222222</v>
       </c>
       <c r="AZ26" t="n">
-        <v>22222222.22222222</v>
+        <v>2222222.222222222</v>
       </c>
       <c r="BA26" t="n">
-        <v>2222222.222222222</v>
+        <v>3333333.333333333</v>
       </c>
       <c r="BB26" t="n">
-        <v>3333333.333333333</v>
+        <v>14583333.33333333</v>
       </c>
       <c r="BC26" t="n">
-        <v>14583333.33333333</v>
+        <v>184790095</v>
       </c>
       <c r="BD26" t="n">
-        <v>184790095</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>20625000</v>
       </c>
       <c r="BF26" t="n">
-        <v>20625000</v>
+        <v>4000000</v>
       </c>
       <c r="BG26" t="n">
-        <v>4000000</v>
+        <v>0</v>
       </c>
       <c r="BH26" t="n">
         <v>0</v>
@@ -9681,10 +9604,10 @@
         <v>0</v>
       </c>
       <c r="BK26" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="BL26" t="n">
-        <v>5000000</v>
+        <v>416666.6666666666</v>
       </c>
       <c r="BM26" t="n">
         <v>416666.6666666666</v>
@@ -9693,85 +9616,85 @@
         <v>416666.6666666666</v>
       </c>
       <c r="BO26" t="n">
-        <v>416666.6666666666</v>
+        <v>0</v>
       </c>
       <c r="BP26" t="n">
-        <v>0</v>
+        <v>50016666.66666666</v>
       </c>
       <c r="BQ26" t="n">
-        <v>50016666.66666666</v>
+        <v>4166666.666666667</v>
       </c>
       <c r="BR26" t="n">
-        <v>4166666.666666667</v>
+        <v>363333.3333333333</v>
       </c>
       <c r="BS26" t="n">
-        <v>363333.3333333333</v>
+        <v>59144455.75</v>
       </c>
       <c r="BT26" t="n">
-        <v>59144455.75</v>
+        <v>0</v>
       </c>
       <c r="BU26" t="n">
-        <v>0</v>
+        <v>10500000</v>
       </c>
       <c r="BV26" t="n">
-        <v>10500000</v>
+        <v>55000000</v>
       </c>
       <c r="BW26" t="n">
-        <v>55000000</v>
+        <v>11111111.11111111</v>
       </c>
       <c r="BX26" t="n">
-        <v>11111111.11111111</v>
+        <v>196153846.1538461</v>
       </c>
       <c r="BY26" t="n">
-        <v>196153846.1538461</v>
+        <v>229166.6666666667</v>
       </c>
       <c r="BZ26" t="n">
-        <v>229166.6666666667</v>
+        <v>19166666.66666667</v>
       </c>
       <c r="CA26" t="n">
-        <v>19166666.66666667</v>
+        <v>40000000</v>
       </c>
       <c r="CB26" t="n">
-        <v>40000000</v>
+        <v>158371040.7239819</v>
       </c>
       <c r="CC26" t="n">
-        <v>158371040.7239819</v>
+        <v>20000000</v>
       </c>
       <c r="CD26" t="n">
-        <v>20000000</v>
+        <v>27500000</v>
       </c>
       <c r="CE26" t="n">
-        <v>27500000</v>
+        <v>13750000</v>
       </c>
       <c r="CF26" t="n">
-        <v>13750000</v>
+        <v>8333333.333333334</v>
       </c>
       <c r="CG26" t="n">
-        <v>8333333.333333334</v>
+        <v>38547677.66666666</v>
       </c>
       <c r="CH26" t="n">
-        <v>38547677.66666666</v>
+        <v>23400000</v>
       </c>
       <c r="CI26" t="n">
-        <v>23400000</v>
+        <v>12500000</v>
       </c>
       <c r="CJ26" t="n">
-        <v>12500000</v>
+        <v>221982973.8571428</v>
       </c>
       <c r="CK26" t="n">
-        <v>221982973.8571428</v>
+        <v>61000000</v>
       </c>
       <c r="CL26" t="n">
-        <v>61000000</v>
+        <v>2199274.388888889</v>
       </c>
       <c r="CM26" t="n">
-        <v>2199274.388888889</v>
+        <v>5909090.909090909</v>
       </c>
       <c r="CN26" t="n">
-        <v>5909090.909090909</v>
+        <v>125000000</v>
       </c>
       <c r="CO26" t="n">
-        <v>125000000</v>
+        <v>0</v>
       </c>
       <c r="CP26" t="n">
         <v>0</v>
@@ -9840,9 +9763,6 @@
         <v>0</v>
       </c>
       <c r="DL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10007,22 +9927,22 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>9722222.222222222</v>
       </c>
       <c r="BC27" t="n">
-        <v>9722222.222222222</v>
+        <v>123193396.6666667</v>
       </c>
       <c r="BD27" t="n">
-        <v>123193396.6666667</v>
+        <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>20625000</v>
       </c>
       <c r="BF27" t="n">
-        <v>20625000</v>
+        <v>4000000</v>
       </c>
       <c r="BG27" t="n">
-        <v>4000000</v>
+        <v>0</v>
       </c>
       <c r="BH27" t="n">
         <v>0</v>
@@ -10034,10 +9954,10 @@
         <v>0</v>
       </c>
       <c r="BK27" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="BL27" t="n">
-        <v>5000000</v>
+        <v>416666.6666666666</v>
       </c>
       <c r="BM27" t="n">
         <v>416666.6666666666</v>
@@ -10046,91 +9966,91 @@
         <v>416666.6666666666</v>
       </c>
       <c r="BO27" t="n">
-        <v>416666.6666666666</v>
+        <v>0</v>
       </c>
       <c r="BP27" t="n">
-        <v>0</v>
+        <v>50016666.66666666</v>
       </c>
       <c r="BQ27" t="n">
-        <v>50016666.66666666</v>
+        <v>4166666.666666667</v>
       </c>
       <c r="BR27" t="n">
-        <v>4166666.666666667</v>
+        <v>363333.3333333333</v>
       </c>
       <c r="BS27" t="n">
-        <v>363333.3333333333</v>
+        <v>59144455.75</v>
       </c>
       <c r="BT27" t="n">
-        <v>59144455.75</v>
+        <v>0</v>
       </c>
       <c r="BU27" t="n">
-        <v>0</v>
+        <v>10500000</v>
       </c>
       <c r="BV27" t="n">
-        <v>10500000</v>
+        <v>55000000</v>
       </c>
       <c r="BW27" t="n">
-        <v>55000000</v>
+        <v>11111111.11111111</v>
       </c>
       <c r="BX27" t="n">
-        <v>11111111.11111111</v>
+        <v>65384615.38461538</v>
       </c>
       <c r="BY27" t="n">
-        <v>65384615.38461538</v>
+        <v>229166.6666666667</v>
       </c>
       <c r="BZ27" t="n">
-        <v>229166.6666666667</v>
+        <v>19166666.66666667</v>
       </c>
       <c r="CA27" t="n">
-        <v>19166666.66666667</v>
+        <v>40000000</v>
       </c>
       <c r="CB27" t="n">
-        <v>40000000</v>
+        <v>158371040.7239819</v>
       </c>
       <c r="CC27" t="n">
-        <v>158371040.7239819</v>
+        <v>20000000</v>
       </c>
       <c r="CD27" t="n">
-        <v>20000000</v>
+        <v>27500000</v>
       </c>
       <c r="CE27" t="n">
-        <v>27500000</v>
+        <v>13750000</v>
       </c>
       <c r="CF27" t="n">
-        <v>13750000</v>
+        <v>8333333.333333334</v>
       </c>
       <c r="CG27" t="n">
-        <v>8333333.333333334</v>
+        <v>38547677.66666666</v>
       </c>
       <c r="CH27" t="n">
-        <v>38547677.66666666</v>
+        <v>23400000</v>
       </c>
       <c r="CI27" t="n">
-        <v>23400000</v>
+        <v>52500000</v>
       </c>
       <c r="CJ27" t="n">
-        <v>52500000</v>
+        <v>221982973.8571428</v>
       </c>
       <c r="CK27" t="n">
-        <v>221982973.8571428</v>
+        <v>61000000</v>
       </c>
       <c r="CL27" t="n">
-        <v>61000000</v>
+        <v>3298911.583333333</v>
       </c>
       <c r="CM27" t="n">
-        <v>3298911.583333333</v>
+        <v>17727272.72727273</v>
       </c>
       <c r="CN27" t="n">
-        <v>17727272.72727273</v>
+        <v>375000000</v>
       </c>
       <c r="CO27" t="n">
-        <v>375000000</v>
+        <v>60666666.66666667</v>
       </c>
       <c r="CP27" t="n">
-        <v>60666666.66666667</v>
+        <v>19833333.33333333</v>
       </c>
       <c r="CQ27" t="n">
-        <v>19833333.33333333</v>
+        <v>0</v>
       </c>
       <c r="CR27" t="n">
         <v>0</v>
@@ -10193,9 +10113,6 @@
         <v>0</v>
       </c>
       <c r="DL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10369,13 +10286,13 @@
         <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>13750000</v>
       </c>
       <c r="BF28" t="n">
-        <v>13750000</v>
+        <v>4000000</v>
       </c>
       <c r="BG28" t="n">
-        <v>4000000</v>
+        <v>0</v>
       </c>
       <c r="BH28" t="n">
         <v>0</v>
@@ -10387,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="BK28" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="BL28" t="n">
-        <v>5000000</v>
+        <v>416666.6666666666</v>
       </c>
       <c r="BM28" t="n">
         <v>416666.6666666666</v>
@@ -10399,91 +10316,91 @@
         <v>416666.6666666666</v>
       </c>
       <c r="BO28" t="n">
-        <v>416666.6666666666</v>
+        <v>0</v>
       </c>
       <c r="BP28" t="n">
-        <v>0</v>
+        <v>50016666.66666666</v>
       </c>
       <c r="BQ28" t="n">
-        <v>50016666.66666666</v>
+        <v>4166666.666666667</v>
       </c>
       <c r="BR28" t="n">
-        <v>4166666.666666667</v>
+        <v>363333.3333333333</v>
       </c>
       <c r="BS28" t="n">
-        <v>363333.3333333333</v>
+        <v>59144455.75</v>
       </c>
       <c r="BT28" t="n">
-        <v>59144455.75</v>
+        <v>0</v>
       </c>
       <c r="BU28" t="n">
-        <v>0</v>
+        <v>10500000</v>
       </c>
       <c r="BV28" t="n">
-        <v>10500000</v>
+        <v>55000000</v>
       </c>
       <c r="BW28" t="n">
-        <v>55000000</v>
+        <v>11111111.11111111</v>
       </c>
       <c r="BX28" t="n">
-        <v>11111111.11111111</v>
+        <v>0</v>
       </c>
       <c r="BY28" t="n">
-        <v>0</v>
+        <v>229166.6666666667</v>
       </c>
       <c r="BZ28" t="n">
-        <v>229166.6666666667</v>
+        <v>19166666.66666667</v>
       </c>
       <c r="CA28" t="n">
-        <v>19166666.66666667</v>
+        <v>26666666.66666667</v>
       </c>
       <c r="CB28" t="n">
-        <v>26666666.66666667</v>
+        <v>158371040.7239819</v>
       </c>
       <c r="CC28" t="n">
-        <v>158371040.7239819</v>
+        <v>20000000</v>
       </c>
       <c r="CD28" t="n">
-        <v>20000000</v>
+        <v>27500000</v>
       </c>
       <c r="CE28" t="n">
-        <v>27500000</v>
+        <v>13750000</v>
       </c>
       <c r="CF28" t="n">
-        <v>13750000</v>
+        <v>8333333.333333334</v>
       </c>
       <c r="CG28" t="n">
-        <v>8333333.333333334</v>
+        <v>38547677.66666666</v>
       </c>
       <c r="CH28" t="n">
-        <v>38547677.66666666</v>
+        <v>23400000</v>
       </c>
       <c r="CI28" t="n">
-        <v>23400000</v>
+        <v>132500000</v>
       </c>
       <c r="CJ28" t="n">
-        <v>132500000</v>
+        <v>221982973.8571428</v>
       </c>
       <c r="CK28" t="n">
-        <v>221982973.8571428</v>
+        <v>61000000</v>
       </c>
       <c r="CL28" t="n">
-        <v>61000000</v>
+        <v>3298911.583333333</v>
       </c>
       <c r="CM28" t="n">
-        <v>3298911.583333333</v>
+        <v>17727272.72727273</v>
       </c>
       <c r="CN28" t="n">
-        <v>17727272.72727273</v>
+        <v>375000000</v>
       </c>
       <c r="CO28" t="n">
-        <v>375000000</v>
+        <v>60666666.66666667</v>
       </c>
       <c r="CP28" t="n">
-        <v>60666666.66666667</v>
+        <v>19833333.33333333</v>
       </c>
       <c r="CQ28" t="n">
-        <v>19833333.33333333</v>
+        <v>0</v>
       </c>
       <c r="CR28" t="n">
         <v>0</v>
@@ -10546,9 +10463,6 @@
         <v>0</v>
       </c>
       <c r="DL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10740,10 +10654,10 @@
         <v>0</v>
       </c>
       <c r="BK29" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="BL29" t="n">
-        <v>5000000</v>
+        <v>416666.6666666666</v>
       </c>
       <c r="BM29" t="n">
         <v>416666.6666666666</v>
@@ -10752,100 +10666,100 @@
         <v>416666.6666666666</v>
       </c>
       <c r="BO29" t="n">
-        <v>416666.6666666666</v>
+        <v>0</v>
       </c>
       <c r="BP29" t="n">
-        <v>0</v>
+        <v>50016666.66666666</v>
       </c>
       <c r="BQ29" t="n">
-        <v>50016666.66666666</v>
+        <v>4166666.666666667</v>
       </c>
       <c r="BR29" t="n">
-        <v>4166666.666666667</v>
+        <v>363333.3333333333</v>
       </c>
       <c r="BS29" t="n">
-        <v>363333.3333333333</v>
+        <v>59144455.75</v>
       </c>
       <c r="BT29" t="n">
-        <v>59144455.75</v>
+        <v>0</v>
       </c>
       <c r="BU29" t="n">
-        <v>0</v>
+        <v>10500000</v>
       </c>
       <c r="BV29" t="n">
-        <v>10500000</v>
+        <v>55000000</v>
       </c>
       <c r="BW29" t="n">
-        <v>55000000</v>
+        <v>11111111.11111111</v>
       </c>
       <c r="BX29" t="n">
-        <v>11111111.11111111</v>
+        <v>0</v>
       </c>
       <c r="BY29" t="n">
-        <v>0</v>
+        <v>229166.6666666667</v>
       </c>
       <c r="BZ29" t="n">
-        <v>229166.6666666667</v>
+        <v>19166666.66666667</v>
       </c>
       <c r="CA29" t="n">
-        <v>19166666.66666667</v>
+        <v>0</v>
       </c>
       <c r="CB29" t="n">
-        <v>0</v>
+        <v>158371040.7239819</v>
       </c>
       <c r="CC29" t="n">
-        <v>158371040.7239819</v>
+        <v>20000000</v>
       </c>
       <c r="CD29" t="n">
-        <v>20000000</v>
+        <v>27500000</v>
       </c>
       <c r="CE29" t="n">
-        <v>27500000</v>
+        <v>13750000</v>
       </c>
       <c r="CF29" t="n">
-        <v>13750000</v>
+        <v>8333333.333333334</v>
       </c>
       <c r="CG29" t="n">
-        <v>8333333.333333334</v>
+        <v>38547677.66666666</v>
       </c>
       <c r="CH29" t="n">
-        <v>38547677.66666666</v>
+        <v>23400000</v>
       </c>
       <c r="CI29" t="n">
-        <v>23400000</v>
+        <v>132500000</v>
       </c>
       <c r="CJ29" t="n">
-        <v>132500000</v>
+        <v>221982973.8571428</v>
       </c>
       <c r="CK29" t="n">
-        <v>221982973.8571428</v>
+        <v>61000000</v>
       </c>
       <c r="CL29" t="n">
-        <v>61000000</v>
+        <v>3298911.583333333</v>
       </c>
       <c r="CM29" t="n">
-        <v>3298911.583333333</v>
+        <v>17727272.72727273</v>
       </c>
       <c r="CN29" t="n">
-        <v>17727272.72727273</v>
+        <v>375000000</v>
       </c>
       <c r="CO29" t="n">
-        <v>375000000</v>
+        <v>60666666.66666667</v>
       </c>
       <c r="CP29" t="n">
-        <v>60666666.66666667</v>
+        <v>19833333.33333333</v>
       </c>
       <c r="CQ29" t="n">
-        <v>19833333.33333333</v>
+        <v>0</v>
       </c>
       <c r="CR29" t="n">
-        <v>0</v>
+        <v>80881609.58333333</v>
       </c>
       <c r="CS29" t="n">
-        <v>80881609.58333333</v>
+        <v>136842105.2631579</v>
       </c>
       <c r="CT29" t="n">
-        <v>136842105.2631579</v>
+        <v>0</v>
       </c>
       <c r="CU29" t="n">
         <v>0</v>
@@ -10899,9 +10813,6 @@
         <v>0</v>
       </c>
       <c r="DL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11093,10 +11004,10 @@
         <v>0</v>
       </c>
       <c r="BK30" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="BL30" t="n">
-        <v>5000000</v>
+        <v>416666.6666666666</v>
       </c>
       <c r="BM30" t="n">
         <v>416666.6666666666</v>
@@ -11105,103 +11016,103 @@
         <v>416666.6666666666</v>
       </c>
       <c r="BO30" t="n">
-        <v>416666.6666666666</v>
+        <v>0</v>
       </c>
       <c r="BP30" t="n">
-        <v>0</v>
+        <v>50016666.66666666</v>
       </c>
       <c r="BQ30" t="n">
-        <v>50016666.66666666</v>
+        <v>4166666.666666667</v>
       </c>
       <c r="BR30" t="n">
-        <v>4166666.666666667</v>
+        <v>363333.3333333333</v>
       </c>
       <c r="BS30" t="n">
-        <v>363333.3333333333</v>
+        <v>59144455.75</v>
       </c>
       <c r="BT30" t="n">
-        <v>59144455.75</v>
+        <v>0</v>
       </c>
       <c r="BU30" t="n">
-        <v>0</v>
+        <v>10500000</v>
       </c>
       <c r="BV30" t="n">
-        <v>10500000</v>
+        <v>55000000</v>
       </c>
       <c r="BW30" t="n">
-        <v>55000000</v>
+        <v>11111111.11111111</v>
       </c>
       <c r="BX30" t="n">
-        <v>11111111.11111111</v>
+        <v>0</v>
       </c>
       <c r="BY30" t="n">
-        <v>0</v>
+        <v>229166.6666666667</v>
       </c>
       <c r="BZ30" t="n">
-        <v>229166.6666666667</v>
+        <v>19166666.66666667</v>
       </c>
       <c r="CA30" t="n">
-        <v>19166666.66666667</v>
+        <v>0</v>
       </c>
       <c r="CB30" t="n">
-        <v>0</v>
+        <v>158371040.7239819</v>
       </c>
       <c r="CC30" t="n">
-        <v>158371040.7239819</v>
+        <v>20000000</v>
       </c>
       <c r="CD30" t="n">
-        <v>20000000</v>
+        <v>27500000</v>
       </c>
       <c r="CE30" t="n">
-        <v>27500000</v>
+        <v>13750000</v>
       </c>
       <c r="CF30" t="n">
-        <v>13750000</v>
+        <v>8333333.333333334</v>
       </c>
       <c r="CG30" t="n">
-        <v>8333333.333333334</v>
+        <v>38547677.66666666</v>
       </c>
       <c r="CH30" t="n">
-        <v>38547677.66666666</v>
+        <v>23400000</v>
       </c>
       <c r="CI30" t="n">
-        <v>23400000</v>
+        <v>132500000</v>
       </c>
       <c r="CJ30" t="n">
-        <v>132500000</v>
+        <v>221982973.8571428</v>
       </c>
       <c r="CK30" t="n">
-        <v>221982973.8571428</v>
+        <v>61000000</v>
       </c>
       <c r="CL30" t="n">
-        <v>61000000</v>
+        <v>3298911.583333333</v>
       </c>
       <c r="CM30" t="n">
-        <v>3298911.583333333</v>
+        <v>17727272.72727273</v>
       </c>
       <c r="CN30" t="n">
-        <v>17727272.72727273</v>
+        <v>375000000</v>
       </c>
       <c r="CO30" t="n">
-        <v>375000000</v>
+        <v>60666666.66666667</v>
       </c>
       <c r="CP30" t="n">
-        <v>60666666.66666667</v>
+        <v>19833333.33333333</v>
       </c>
       <c r="CQ30" t="n">
-        <v>19833333.33333333</v>
+        <v>0</v>
       </c>
       <c r="CR30" t="n">
-        <v>0</v>
+        <v>80881609.58333333</v>
       </c>
       <c r="CS30" t="n">
-        <v>80881609.58333333</v>
+        <v>205263157.8947369</v>
       </c>
       <c r="CT30" t="n">
-        <v>205263157.8947369</v>
+        <v>258758991.8888889</v>
       </c>
       <c r="CU30" t="n">
-        <v>258758991.8888889</v>
+        <v>0</v>
       </c>
       <c r="CV30" t="n">
         <v>0</v>
@@ -11252,9 +11163,6 @@
         <v>0</v>
       </c>
       <c r="DL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11449,7 +11357,7 @@
         <v>0</v>
       </c>
       <c r="BL31" t="n">
-        <v>0</v>
+        <v>138888.8888888889</v>
       </c>
       <c r="BM31" t="n">
         <v>138888.8888888889</v>
@@ -11458,112 +11366,112 @@
         <v>138888.8888888889</v>
       </c>
       <c r="BO31" t="n">
-        <v>138888.8888888889</v>
+        <v>0</v>
       </c>
       <c r="BP31" t="n">
-        <v>0</v>
+        <v>50016666.66666666</v>
       </c>
       <c r="BQ31" t="n">
-        <v>50016666.66666666</v>
+        <v>4166666.666666667</v>
       </c>
       <c r="BR31" t="n">
-        <v>4166666.666666667</v>
+        <v>363333.3333333333</v>
       </c>
       <c r="BS31" t="n">
-        <v>363333.3333333333</v>
+        <v>59144455.75</v>
       </c>
       <c r="BT31" t="n">
-        <v>59144455.75</v>
+        <v>0</v>
       </c>
       <c r="BU31" t="n">
-        <v>0</v>
+        <v>10500000</v>
       </c>
       <c r="BV31" t="n">
-        <v>10500000</v>
+        <v>55000000</v>
       </c>
       <c r="BW31" t="n">
-        <v>55000000</v>
+        <v>74269005.84795323</v>
       </c>
       <c r="BX31" t="n">
-        <v>74269005.84795323</v>
+        <v>0</v>
       </c>
       <c r="BY31" t="n">
-        <v>0</v>
+        <v>229166.6666666667</v>
       </c>
       <c r="BZ31" t="n">
-        <v>229166.6666666667</v>
+        <v>19166666.66666667</v>
       </c>
       <c r="CA31" t="n">
-        <v>19166666.66666667</v>
+        <v>0</v>
       </c>
       <c r="CB31" t="n">
-        <v>0</v>
+        <v>158371040.7239819</v>
       </c>
       <c r="CC31" t="n">
-        <v>158371040.7239819</v>
+        <v>20000000</v>
       </c>
       <c r="CD31" t="n">
-        <v>20000000</v>
+        <v>27500000</v>
       </c>
       <c r="CE31" t="n">
-        <v>27500000</v>
+        <v>13750000</v>
       </c>
       <c r="CF31" t="n">
-        <v>13750000</v>
+        <v>8333333.333333334</v>
       </c>
       <c r="CG31" t="n">
-        <v>8333333.333333334</v>
+        <v>38547677.66666666</v>
       </c>
       <c r="CH31" t="n">
-        <v>38547677.66666666</v>
+        <v>23400000</v>
       </c>
       <c r="CI31" t="n">
-        <v>23400000</v>
+        <v>132500000</v>
       </c>
       <c r="CJ31" t="n">
-        <v>132500000</v>
+        <v>221982973.8571428</v>
       </c>
       <c r="CK31" t="n">
-        <v>221982973.8571428</v>
+        <v>61000000</v>
       </c>
       <c r="CL31" t="n">
-        <v>61000000</v>
+        <v>3298911.583333333</v>
       </c>
       <c r="CM31" t="n">
-        <v>3298911.583333333</v>
+        <v>17727272.72727273</v>
       </c>
       <c r="CN31" t="n">
-        <v>17727272.72727273</v>
+        <v>375000000</v>
       </c>
       <c r="CO31" t="n">
-        <v>375000000</v>
+        <v>60666666.66666667</v>
       </c>
       <c r="CP31" t="n">
-        <v>60666666.66666667</v>
+        <v>19833333.33333333</v>
       </c>
       <c r="CQ31" t="n">
-        <v>19833333.33333333</v>
+        <v>0</v>
       </c>
       <c r="CR31" t="n">
-        <v>0</v>
+        <v>80881609.58333333</v>
       </c>
       <c r="CS31" t="n">
-        <v>80881609.58333333</v>
+        <v>205263157.8947369</v>
       </c>
       <c r="CT31" t="n">
-        <v>205263157.8947369</v>
+        <v>388138487.8333334</v>
       </c>
       <c r="CU31" t="n">
-        <v>388138487.8333334</v>
+        <v>10000000</v>
       </c>
       <c r="CV31" t="n">
-        <v>10000000</v>
+        <v>33333333.33333334</v>
       </c>
       <c r="CW31" t="n">
-        <v>33333333.33333334</v>
+        <v>100000000</v>
       </c>
       <c r="CX31" t="n">
-        <v>100000000</v>
+        <v>0</v>
       </c>
       <c r="CY31" t="n">
         <v>0</v>
@@ -11605,9 +11513,6 @@
         <v>0</v>
       </c>
       <c r="DL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11814,121 +11719,121 @@
         <v>0</v>
       </c>
       <c r="BP32" t="n">
-        <v>0</v>
+        <v>50005555.55555555</v>
       </c>
       <c r="BQ32" t="n">
-        <v>50005555.55555555</v>
+        <v>2777777.777777778</v>
       </c>
       <c r="BR32" t="n">
-        <v>2777777.777777778</v>
+        <v>242222.2222222222</v>
       </c>
       <c r="BS32" t="n">
-        <v>242222.2222222222</v>
+        <v>59144455.75</v>
       </c>
       <c r="BT32" t="n">
-        <v>59144455.75</v>
+        <v>0</v>
       </c>
       <c r="BU32" t="n">
-        <v>0</v>
+        <v>10500000</v>
       </c>
       <c r="BV32" t="n">
-        <v>10500000</v>
+        <v>55000000</v>
       </c>
       <c r="BW32" t="n">
-        <v>55000000</v>
+        <v>74269005.84795323</v>
       </c>
       <c r="BX32" t="n">
-        <v>74269005.84795323</v>
+        <v>0</v>
       </c>
       <c r="BY32" t="n">
-        <v>0</v>
+        <v>229166.6666666667</v>
       </c>
       <c r="BZ32" t="n">
-        <v>229166.6666666667</v>
+        <v>19166666.66666667</v>
       </c>
       <c r="CA32" t="n">
-        <v>19166666.66666667</v>
+        <v>0</v>
       </c>
       <c r="CB32" t="n">
-        <v>0</v>
+        <v>158371040.7239819</v>
       </c>
       <c r="CC32" t="n">
-        <v>158371040.7239819</v>
+        <v>20000000</v>
       </c>
       <c r="CD32" t="n">
-        <v>20000000</v>
+        <v>27500000</v>
       </c>
       <c r="CE32" t="n">
-        <v>27500000</v>
+        <v>13750000</v>
       </c>
       <c r="CF32" t="n">
-        <v>13750000</v>
+        <v>8333333.333333334</v>
       </c>
       <c r="CG32" t="n">
-        <v>8333333.333333334</v>
+        <v>38547677.66666666</v>
       </c>
       <c r="CH32" t="n">
-        <v>38547677.66666666</v>
+        <v>23400000</v>
       </c>
       <c r="CI32" t="n">
-        <v>23400000</v>
+        <v>132500000</v>
       </c>
       <c r="CJ32" t="n">
-        <v>132500000</v>
+        <v>73994324.61904761</v>
       </c>
       <c r="CK32" t="n">
-        <v>73994324.61904761</v>
+        <v>20333333.33333333</v>
       </c>
       <c r="CL32" t="n">
-        <v>20333333.33333333</v>
+        <v>3298911.583333333</v>
       </c>
       <c r="CM32" t="n">
-        <v>3298911.583333333</v>
+        <v>17727272.72727273</v>
       </c>
       <c r="CN32" t="n">
-        <v>17727272.72727273</v>
+        <v>375000000</v>
       </c>
       <c r="CO32" t="n">
-        <v>375000000</v>
+        <v>60666666.66666667</v>
       </c>
       <c r="CP32" t="n">
-        <v>60666666.66666667</v>
+        <v>19833333.33333333</v>
       </c>
       <c r="CQ32" t="n">
-        <v>19833333.33333333</v>
+        <v>0</v>
       </c>
       <c r="CR32" t="n">
-        <v>0</v>
+        <v>80881609.58333333</v>
       </c>
       <c r="CS32" t="n">
-        <v>80881609.58333333</v>
+        <v>205263157.8947369</v>
       </c>
       <c r="CT32" t="n">
-        <v>205263157.8947369</v>
+        <v>388138487.8333334</v>
       </c>
       <c r="CU32" t="n">
-        <v>388138487.8333334</v>
+        <v>10000000</v>
       </c>
       <c r="CV32" t="n">
-        <v>10000000</v>
+        <v>33333333.33333334</v>
       </c>
       <c r="CW32" t="n">
-        <v>33333333.33333334</v>
+        <v>100000000</v>
       </c>
       <c r="CX32" t="n">
-        <v>100000000</v>
+        <v>0</v>
       </c>
       <c r="CY32" t="n">
-        <v>0</v>
+        <v>85310997.33333334</v>
       </c>
       <c r="CZ32" t="n">
-        <v>85310997.33333334</v>
+        <v>19311307.58333334</v>
       </c>
       <c r="DA32" t="n">
-        <v>19311307.58333334</v>
+        <v>1251565.583333333</v>
       </c>
       <c r="DB32" t="n">
-        <v>1251565.583333333</v>
+        <v>0</v>
       </c>
       <c r="DC32" t="n">
         <v>0</v>
@@ -11958,9 +11863,6 @@
         <v>0</v>
       </c>
       <c r="DL32" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12167,10 +12069,10 @@
         <v>0</v>
       </c>
       <c r="BP33" t="n">
-        <v>0</v>
+        <v>50000000</v>
       </c>
       <c r="BQ33" t="n">
-        <v>50000000</v>
+        <v>0</v>
       </c>
       <c r="BR33" t="n">
         <v>0</v>
@@ -12182,112 +12084,112 @@
         <v>0</v>
       </c>
       <c r="BU33" t="n">
-        <v>0</v>
+        <v>7000000</v>
       </c>
       <c r="BV33" t="n">
-        <v>7000000</v>
+        <v>36666666.66666666</v>
       </c>
       <c r="BW33" t="n">
-        <v>36666666.66666666</v>
+        <v>74269005.84795323</v>
       </c>
       <c r="BX33" t="n">
-        <v>74269005.84795323</v>
+        <v>0</v>
       </c>
       <c r="BY33" t="n">
-        <v>0</v>
+        <v>229166.6666666667</v>
       </c>
       <c r="BZ33" t="n">
-        <v>229166.6666666667</v>
+        <v>19166666.66666667</v>
       </c>
       <c r="CA33" t="n">
-        <v>19166666.66666667</v>
+        <v>0</v>
       </c>
       <c r="CB33" t="n">
-        <v>0</v>
+        <v>158371040.7239819</v>
       </c>
       <c r="CC33" t="n">
-        <v>158371040.7239819</v>
+        <v>20000000</v>
       </c>
       <c r="CD33" t="n">
-        <v>20000000</v>
+        <v>27500000</v>
       </c>
       <c r="CE33" t="n">
-        <v>27500000</v>
+        <v>13750000</v>
       </c>
       <c r="CF33" t="n">
-        <v>13750000</v>
+        <v>8333333.333333334</v>
       </c>
       <c r="CG33" t="n">
-        <v>8333333.333333334</v>
+        <v>38547677.66666666</v>
       </c>
       <c r="CH33" t="n">
-        <v>38547677.66666666</v>
+        <v>0</v>
       </c>
       <c r="CI33" t="n">
-        <v>0</v>
+        <v>132500000</v>
       </c>
       <c r="CJ33" t="n">
-        <v>132500000</v>
+        <v>0</v>
       </c>
       <c r="CK33" t="n">
         <v>0</v>
       </c>
       <c r="CL33" t="n">
-        <v>0</v>
+        <v>3298911.583333333</v>
       </c>
       <c r="CM33" t="n">
-        <v>3298911.583333333</v>
+        <v>17727272.72727273</v>
       </c>
       <c r="CN33" t="n">
-        <v>17727272.72727273</v>
+        <v>375000000</v>
       </c>
       <c r="CO33" t="n">
-        <v>375000000</v>
+        <v>60666666.66666667</v>
       </c>
       <c r="CP33" t="n">
-        <v>60666666.66666667</v>
+        <v>19833333.33333333</v>
       </c>
       <c r="CQ33" t="n">
-        <v>19833333.33333333</v>
+        <v>0</v>
       </c>
       <c r="CR33" t="n">
-        <v>0</v>
+        <v>80881609.58333333</v>
       </c>
       <c r="CS33" t="n">
-        <v>80881609.58333333</v>
+        <v>205263157.8947369</v>
       </c>
       <c r="CT33" t="n">
-        <v>205263157.8947369</v>
+        <v>388138487.8333334</v>
       </c>
       <c r="CU33" t="n">
-        <v>388138487.8333334</v>
+        <v>10000000</v>
       </c>
       <c r="CV33" t="n">
-        <v>10000000</v>
+        <v>33333333.33333334</v>
       </c>
       <c r="CW33" t="n">
-        <v>33333333.33333334</v>
+        <v>100000000</v>
       </c>
       <c r="CX33" t="n">
-        <v>100000000</v>
+        <v>0</v>
       </c>
       <c r="CY33" t="n">
-        <v>0</v>
+        <v>85310997.33333334</v>
       </c>
       <c r="CZ33" t="n">
-        <v>85310997.33333334</v>
+        <v>19311307.58333334</v>
       </c>
       <c r="DA33" t="n">
-        <v>19311307.58333334</v>
+        <v>1251565.583333333</v>
       </c>
       <c r="DB33" t="n">
-        <v>1251565.583333333</v>
+        <v>40000000</v>
       </c>
       <c r="DC33" t="n">
-        <v>40000000</v>
+        <v>34166666.66666666</v>
       </c>
       <c r="DD33" t="n">
-        <v>34166666.66666666</v>
+        <v>0</v>
       </c>
       <c r="DE33" t="n">
         <v>0</v>
@@ -12311,9 +12213,6 @@
         <v>0</v>
       </c>
       <c r="DL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12520,10 +12419,10 @@
         <v>0</v>
       </c>
       <c r="BP34" t="n">
-        <v>0</v>
+        <v>50000000</v>
       </c>
       <c r="BQ34" t="n">
-        <v>50000000</v>
+        <v>0</v>
       </c>
       <c r="BR34" t="n">
         <v>0</v>
@@ -12538,115 +12437,115 @@
         <v>0</v>
       </c>
       <c r="BV34" t="n">
-        <v>0</v>
+        <v>218519052.6666667</v>
       </c>
       <c r="BW34" t="n">
-        <v>218519052.6666667</v>
+        <v>74269005.84795323</v>
       </c>
       <c r="BX34" t="n">
-        <v>74269005.84795323</v>
+        <v>0</v>
       </c>
       <c r="BY34" t="n">
-        <v>0</v>
+        <v>229166.6666666667</v>
       </c>
       <c r="BZ34" t="n">
-        <v>229166.6666666667</v>
+        <v>19166666.66666667</v>
       </c>
       <c r="CA34" t="n">
-        <v>19166666.66666667</v>
+        <v>0</v>
       </c>
       <c r="CB34" t="n">
-        <v>0</v>
+        <v>158371040.7239819</v>
       </c>
       <c r="CC34" t="n">
-        <v>158371040.7239819</v>
+        <v>20000000</v>
       </c>
       <c r="CD34" t="n">
-        <v>20000000</v>
+        <v>27500000</v>
       </c>
       <c r="CE34" t="n">
-        <v>27500000</v>
+        <v>13750000</v>
       </c>
       <c r="CF34" t="n">
-        <v>13750000</v>
+        <v>8333333.333333334</v>
       </c>
       <c r="CG34" t="n">
-        <v>8333333.333333334</v>
+        <v>38547677.66666666</v>
       </c>
       <c r="CH34" t="n">
-        <v>38547677.66666666</v>
+        <v>0</v>
       </c>
       <c r="CI34" t="n">
-        <v>0</v>
+        <v>132500000</v>
       </c>
       <c r="CJ34" t="n">
-        <v>132500000</v>
+        <v>0</v>
       </c>
       <c r="CK34" t="n">
         <v>0</v>
       </c>
       <c r="CL34" t="n">
-        <v>0</v>
+        <v>3298911.583333333</v>
       </c>
       <c r="CM34" t="n">
-        <v>3298911.583333333</v>
+        <v>0</v>
       </c>
       <c r="CN34" t="n">
-        <v>0</v>
+        <v>375000000</v>
       </c>
       <c r="CO34" t="n">
-        <v>375000000</v>
+        <v>60666666.66666667</v>
       </c>
       <c r="CP34" t="n">
-        <v>60666666.66666667</v>
+        <v>19833333.33333333</v>
       </c>
       <c r="CQ34" t="n">
-        <v>19833333.33333333</v>
+        <v>0</v>
       </c>
       <c r="CR34" t="n">
-        <v>0</v>
+        <v>80881609.58333333</v>
       </c>
       <c r="CS34" t="n">
-        <v>80881609.58333333</v>
+        <v>205263157.8947369</v>
       </c>
       <c r="CT34" t="n">
-        <v>205263157.8947369</v>
+        <v>388138487.8333334</v>
       </c>
       <c r="CU34" t="n">
-        <v>388138487.8333334</v>
+        <v>10000000</v>
       </c>
       <c r="CV34" t="n">
-        <v>10000000</v>
+        <v>33333333.33333334</v>
       </c>
       <c r="CW34" t="n">
-        <v>33333333.33333334</v>
+        <v>100000000</v>
       </c>
       <c r="CX34" t="n">
-        <v>100000000</v>
+        <v>0</v>
       </c>
       <c r="CY34" t="n">
-        <v>0</v>
+        <v>85310997.33333334</v>
       </c>
       <c r="CZ34" t="n">
-        <v>85310997.33333334</v>
+        <v>19311307.58333334</v>
       </c>
       <c r="DA34" t="n">
-        <v>19311307.58333334</v>
+        <v>1251565.583333333</v>
       </c>
       <c r="DB34" t="n">
-        <v>1251565.583333333</v>
+        <v>60000000</v>
       </c>
       <c r="DC34" t="n">
-        <v>60000000</v>
+        <v>102500000</v>
       </c>
       <c r="DD34" t="n">
-        <v>102500000</v>
+        <v>111111111.1111111</v>
       </c>
       <c r="DE34" t="n">
-        <v>111111111.1111111</v>
+        <v>22222222.22222222</v>
       </c>
       <c r="DF34" t="n">
-        <v>22222222.22222222</v>
+        <v>0</v>
       </c>
       <c r="DG34" t="n">
         <v>0</v>
@@ -12664,9 +12563,6 @@
         <v>0</v>
       </c>
       <c r="DL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12873,10 +12769,10 @@
         <v>0</v>
       </c>
       <c r="BP35" t="n">
-        <v>0</v>
+        <v>16666666.66666667</v>
       </c>
       <c r="BQ35" t="n">
-        <v>16666666.66666667</v>
+        <v>0</v>
       </c>
       <c r="BR35" t="n">
         <v>0</v>
@@ -12885,141 +12781,138 @@
         <v>0</v>
       </c>
       <c r="BT35" t="n">
-        <v>0</v>
+        <v>50000000</v>
       </c>
       <c r="BU35" t="n">
-        <v>50000000</v>
+        <v>0</v>
       </c>
       <c r="BV35" t="n">
-        <v>0</v>
+        <v>218519052.6666667</v>
       </c>
       <c r="BW35" t="n">
-        <v>218519052.6666667</v>
+        <v>63157894.73684211</v>
       </c>
       <c r="BX35" t="n">
-        <v>63157894.73684211</v>
+        <v>0</v>
       </c>
       <c r="BY35" t="n">
         <v>0</v>
       </c>
       <c r="BZ35" t="n">
-        <v>0</v>
+        <v>6388888.888888889</v>
       </c>
       <c r="CA35" t="n">
-        <v>6388888.888888889</v>
+        <v>0</v>
       </c>
       <c r="CB35" t="n">
-        <v>0</v>
+        <v>158371040.7239819</v>
       </c>
       <c r="CC35" t="n">
-        <v>158371040.7239819</v>
+        <v>13333333.33333333</v>
       </c>
       <c r="CD35" t="n">
-        <v>13333333.33333333</v>
+        <v>27500000</v>
       </c>
       <c r="CE35" t="n">
-        <v>27500000</v>
+        <v>13750000</v>
       </c>
       <c r="CF35" t="n">
-        <v>13750000</v>
+        <v>8333333.333333334</v>
       </c>
       <c r="CG35" t="n">
-        <v>8333333.333333334</v>
+        <v>38547677.66666666</v>
       </c>
       <c r="CH35" t="n">
-        <v>38547677.66666666</v>
+        <v>0</v>
       </c>
       <c r="CI35" t="n">
-        <v>0</v>
+        <v>132500000</v>
       </c>
       <c r="CJ35" t="n">
-        <v>132500000</v>
+        <v>0</v>
       </c>
       <c r="CK35" t="n">
         <v>0</v>
       </c>
       <c r="CL35" t="n">
-        <v>0</v>
+        <v>3298911.583333333</v>
       </c>
       <c r="CM35" t="n">
-        <v>3298911.583333333</v>
+        <v>0</v>
       </c>
       <c r="CN35" t="n">
-        <v>0</v>
+        <v>375000000</v>
       </c>
       <c r="CO35" t="n">
-        <v>375000000</v>
+        <v>60666666.66666667</v>
       </c>
       <c r="CP35" t="n">
-        <v>60666666.66666667</v>
+        <v>19833333.33333333</v>
       </c>
       <c r="CQ35" t="n">
-        <v>19833333.33333333</v>
+        <v>0</v>
       </c>
       <c r="CR35" t="n">
-        <v>0</v>
+        <v>80881609.58333333</v>
       </c>
       <c r="CS35" t="n">
-        <v>80881609.58333333</v>
+        <v>136842105.2631579</v>
       </c>
       <c r="CT35" t="n">
-        <v>136842105.2631579</v>
+        <v>388138487.8333334</v>
       </c>
       <c r="CU35" t="n">
-        <v>388138487.8333334</v>
+        <v>10000000</v>
       </c>
       <c r="CV35" t="n">
-        <v>10000000</v>
+        <v>33333333.33333334</v>
       </c>
       <c r="CW35" t="n">
-        <v>33333333.33333334</v>
+        <v>100000000</v>
       </c>
       <c r="CX35" t="n">
-        <v>100000000</v>
+        <v>0</v>
       </c>
       <c r="CY35" t="n">
-        <v>0</v>
+        <v>85310997.33333334</v>
       </c>
       <c r="CZ35" t="n">
-        <v>85310997.33333334</v>
+        <v>19311307.58333334</v>
       </c>
       <c r="DA35" t="n">
-        <v>19311307.58333334</v>
+        <v>1251565.583333333</v>
       </c>
       <c r="DB35" t="n">
-        <v>1251565.583333333</v>
+        <v>0</v>
       </c>
       <c r="DC35" t="n">
-        <v>0</v>
+        <v>102500000</v>
       </c>
       <c r="DD35" t="n">
-        <v>102500000</v>
+        <v>166666666.6666667</v>
       </c>
       <c r="DE35" t="n">
-        <v>166666666.6666667</v>
+        <v>66666666.66666667</v>
       </c>
       <c r="DF35" t="n">
-        <v>66666666.66666667</v>
+        <v>0</v>
       </c>
       <c r="DG35" t="n">
-        <v>0</v>
+        <v>4666666.666666667</v>
       </c>
       <c r="DH35" t="n">
-        <v>4666666.666666667</v>
+        <v>45833333.33333334</v>
       </c>
       <c r="DI35" t="n">
-        <v>45833333.33333334</v>
+        <v>405555555.5555556</v>
       </c>
       <c r="DJ35" t="n">
-        <v>405555555.5555556</v>
+        <v>44964000</v>
       </c>
       <c r="DK35" t="n">
-        <v>44964000</v>
+        <v>0</v>
       </c>
       <c r="DL35" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13238,19 +13131,19 @@
         <v>0</v>
       </c>
       <c r="BT36" t="n">
-        <v>0</v>
+        <v>75000000</v>
       </c>
       <c r="BU36" t="n">
-        <v>75000000</v>
+        <v>0</v>
       </c>
       <c r="BV36" t="n">
-        <v>0</v>
+        <v>218519052.6666667</v>
       </c>
       <c r="BW36" t="n">
-        <v>218519052.6666667</v>
+        <v>63157894.73684211</v>
       </c>
       <c r="BX36" t="n">
-        <v>63157894.73684211</v>
+        <v>0</v>
       </c>
       <c r="BY36" t="n">
         <v>0</v>
@@ -13262,117 +13155,114 @@
         <v>0</v>
       </c>
       <c r="CB36" t="n">
-        <v>0</v>
+        <v>105580693.8159879</v>
       </c>
       <c r="CC36" t="n">
-        <v>105580693.8159879</v>
+        <v>0</v>
       </c>
       <c r="CD36" t="n">
         <v>0</v>
       </c>
       <c r="CE36" t="n">
-        <v>0</v>
+        <v>4583333.333333333</v>
       </c>
       <c r="CF36" t="n">
-        <v>4583333.333333333</v>
+        <v>2777777.777777778</v>
       </c>
       <c r="CG36" t="n">
-        <v>2777777.777777778</v>
+        <v>25698451.77777778</v>
       </c>
       <c r="CH36" t="n">
-        <v>25698451.77777778</v>
+        <v>0</v>
       </c>
       <c r="CI36" t="n">
-        <v>0</v>
+        <v>12500000</v>
       </c>
       <c r="CJ36" t="n">
-        <v>12500000</v>
+        <v>0</v>
       </c>
       <c r="CK36" t="n">
         <v>0</v>
       </c>
       <c r="CL36" t="n">
-        <v>0</v>
+        <v>3298911.583333333</v>
       </c>
       <c r="CM36" t="n">
-        <v>3298911.583333333</v>
+        <v>0</v>
       </c>
       <c r="CN36" t="n">
-        <v>0</v>
+        <v>375000000</v>
       </c>
       <c r="CO36" t="n">
-        <v>375000000</v>
+        <v>60666666.66666667</v>
       </c>
       <c r="CP36" t="n">
-        <v>60666666.66666667</v>
+        <v>19833333.33333333</v>
       </c>
       <c r="CQ36" t="n">
-        <v>19833333.33333333</v>
+        <v>0</v>
       </c>
       <c r="CR36" t="n">
-        <v>0</v>
+        <v>80881609.58333333</v>
       </c>
       <c r="CS36" t="n">
-        <v>80881609.58333333</v>
+        <v>0</v>
       </c>
       <c r="CT36" t="n">
-        <v>0</v>
+        <v>388138487.8333334</v>
       </c>
       <c r="CU36" t="n">
-        <v>388138487.8333334</v>
+        <v>10000000</v>
       </c>
       <c r="CV36" t="n">
-        <v>10000000</v>
+        <v>33333333.33333334</v>
       </c>
       <c r="CW36" t="n">
-        <v>33333333.33333334</v>
+        <v>100000000</v>
       </c>
       <c r="CX36" t="n">
-        <v>100000000</v>
+        <v>0</v>
       </c>
       <c r="CY36" t="n">
-        <v>0</v>
+        <v>85310997.33333334</v>
       </c>
       <c r="CZ36" t="n">
-        <v>85310997.33333334</v>
+        <v>19311307.58333334</v>
       </c>
       <c r="DA36" t="n">
-        <v>19311307.58333334</v>
+        <v>1251565.583333333</v>
       </c>
       <c r="DB36" t="n">
-        <v>1251565.583333333</v>
+        <v>0</v>
       </c>
       <c r="DC36" t="n">
-        <v>0</v>
+        <v>102500000</v>
       </c>
       <c r="DD36" t="n">
-        <v>102500000</v>
+        <v>166666666.6666667</v>
       </c>
       <c r="DE36" t="n">
-        <v>166666666.6666667</v>
+        <v>66666666.66666667</v>
       </c>
       <c r="DF36" t="n">
-        <v>66666666.66666667</v>
+        <v>0</v>
       </c>
       <c r="DG36" t="n">
-        <v>0</v>
+        <v>4666666.666666667</v>
       </c>
       <c r="DH36" t="n">
-        <v>4666666.666666667</v>
+        <v>45833333.33333334</v>
       </c>
       <c r="DI36" t="n">
-        <v>45833333.33333334</v>
+        <v>608333333.3333334</v>
       </c>
       <c r="DJ36" t="n">
-        <v>608333333.3333334</v>
+        <v>120000000</v>
       </c>
       <c r="DK36" t="n">
-        <v>120000000</v>
+        <v>891666.6666666667</v>
       </c>
       <c r="DL36" t="n">
-        <v>891666.6666666667</v>
-      </c>
-      <c r="DM36" t="n">
         <v>611111.1111111111</v>
       </c>
     </row>
